--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,29 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A652C4E-49F7-0D4D-89B0-88360FD4E66E}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375846A0-4FB5-7649-B7B2-3D8ED3FB6C80}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="2240" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AP$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AP$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="862">
   <si>
     <t>Tipo</t>
   </si>
@@ -2509,9 +2522,6 @@
     <t>[FUN4DATE, BRIDGE-AI, TUCAN6-CM]</t>
   </si>
   <si>
-    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/]</t>
-  </si>
-  <si>
     <t>The proliferation of Generative Artificial Ingelligence (AI), especially Large Language Models, presents transformative opportunities for urban applications through Urban Foundation Models. However, base models face limitations, as they only contain the knowledge available at the time of training, and updating them is both time-consuming and costly. Retrieval Augmented Generation (RAG) has emerged in the literature as the preferred approach for injecting contextual information into Foundation Models. It prevails over techniques such as fine-tuning, which are less effective in dynamic, real-time scenarios like those found in urban environments. However, traditional RAG architectures, based on semantic databases, knowledge graphs, structured data, or AI-powered web searches, do not fully meet the demands of urban contexts. Urban environments are complex systems characterized by large volumes of interconnected data, frequent updates, real-time processing requirements, security needs, and strong links to the physical world. This work proposes a real-time spatial RAG architecture that defines the necessary components for the effective integration of generative AI into cities, leveraging temporal and spatial filtering capabilities through linked data. The proposed architecture is implemented using FIWARE, an ecosystem of software components to develop smart city solutions and digital twins. The design and implementation are demonstrated through the use case of a tourism assistant in the city of Madrid. The use case serves to validate the correct integration of Foundation Models through the proposed RAG architecture.</t>
   </si>
   <si>
@@ -2961,9 +2971,6 @@
     <t>4OULZ7Gr8RgC</t>
   </si>
   <si>
-    <t>https://arxiv.org/abs/2601.06118</t>
-  </si>
-  <si>
     <t>T. Fu, G. Martínez, J. Conde, C. Arriaga, P. Reviriego, X. Qi, S. Liu</t>
   </si>
   <si>
@@ -3129,9 +3136,6 @@
     <t>E. Barra, S. López-Pernas, J. Conde, A. Gordillo</t>
   </si>
   <si>
-    <t xml:space="preserve">	Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
-  </si>
-  <si>
     <t>KxtntwgDAa4C</t>
   </si>
   <si>
@@ -3177,6 +3181,65 @@
   </si>
   <si>
     <t>https://oa.upm.es/97555/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TC.2026.3732142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
+  </si>
+  <si>
+    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/, https://www.linkedin.com/posts/javier-conde-diaz_upm-ngsi-rag-activity-7503435475433545728-YfYa?utm_source=social_share_send&amp;utm_medium=android_app&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+  </si>
+  <si>
+    <t>Evaluating large language models with tests of Spanish as a foreign language: pass or fail?</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/applin/amag048</t>
+  </si>
+  <si>
+    <t>Applied Linguistics</t>
+  </si>
+  <si>
+    <t>Oxford University Press</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 3.9 (26/312 – Q1 [D1])</t>
+  </si>
+  <si>
+    <t>Linguistics - SSCI</t>
+  </si>
+  <si>
+    <t>M. Mayor-Rocher , N. Melero , E. Merino-Gómez , M. Grandury , J. Conde , P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2409.15334, ]</t>
+  </si>
+  <si>
+    <t>[https://zenodo.org/doi/10.5281/zenodo.13643393]</t>
+  </si>
+  <si>
+    <t>Subirlo a archivo digital upm</t>
+  </si>
+  <si>
+    <t>FUN4DATE, SMARTY</t>
+  </si>
+  <si>
+    <t>Large language models (LLMs) have been profusely evaluated on their ability to answer questions on many topics and their performance on different natural language understanding tasks. Those tests are usually conducted in English, but most LLM users are not native English speakers. Therefore, it is of interest to analyse how LLMs understand other languages at different levels: from paragraphs to morphemes. In this paper, we evaluate the performance of state-of-the-art LLMs in TELEIA, a recently released benchmark with similar questions to those of Spanish exams for foreign students, covering topics such as reading comprehension, word formation, meaning and compositional semantics, and grammar. The results show that LLMs perform well at understanding Spanish but are still far from achieving the level of a native speaker in terms of grammatical competence.</t>
+  </si>
+  <si>
+    <t>@article{10.1093/applin/amag048,
+    author = {Mayor-Rocher, Marina and Melero, Nina and Merino-Gómez, Elena and Grandury, María and Conde, Javier and Reviriego, Pedro},
+    title = {Evaluating large language models with tests of Spanish as a foreign language: pass or fail?},
+    journal = {Applied Linguistics},
+    pages = {amag048},
+    year = {2026},
+    month = {09},
+    issn = {0142-6001},
+    doi = {10.1093/applin/amag048},
+    url = {https://doi.org/10.1093/applin/amag048},
+    eprint = {https://academic.oup.com/applij/advance-article-pdf/doi/10.1093/applin/amag048/71017839/amag048.pdf},
+}</t>
   </si>
 </sst>
 </file>
@@ -3402,14 +3465,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3720,9 +3784,13 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
@@ -4090,9 +4158,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="79" customWidth="1"/>
-    <col min="2" max="2" width="20" style="28" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="90" style="37" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" style="37" customWidth="1"/>
     <col min="5" max="5" width="22" style="37" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" style="37" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="37" customWidth="1"/>
@@ -9803,19 +9871,19 @@
         <v>670</v>
       </c>
       <c r="AF59" s="37" t="s">
+        <v>848</v>
+      </c>
+      <c r="AJ59" s="37" t="s">
         <v>671</v>
       </c>
-      <c r="AJ59" s="37" t="s">
+      <c r="AK59" s="95" t="s">
         <v>672</v>
       </c>
-      <c r="AK59" s="95" t="s">
+      <c r="AM59" s="37" t="s">
         <v>673</v>
       </c>
-      <c r="AM59" s="37" t="s">
+      <c r="AO59" s="37" t="s">
         <v>674</v>
-      </c>
-      <c r="AO59" s="37" t="s">
-        <v>675</v>
       </c>
       <c r="AP59"/>
     </row>
@@ -9830,13 +9898,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="63" t="s">
+        <v>675</v>
+      </c>
+      <c r="E60" s="63" t="s">
         <v>676</v>
       </c>
-      <c r="E60" s="63" t="s">
+      <c r="F60" s="108" t="s">
         <v>677</v>
-      </c>
-      <c r="F60" s="108" t="s">
-        <v>678</v>
       </c>
       <c r="G60" s="47" t="s">
         <v>519</v>
@@ -9863,7 +9931,7 @@
         <v>50</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P60" s="65">
         <v>10</v>
@@ -9888,30 +9956,30 @@
         <v>51</v>
       </c>
       <c r="AB60" s="63" t="s">
+        <v>679</v>
+      </c>
+      <c r="AC60" s="108" t="s">
         <v>680</v>
       </c>
-      <c r="AC60" s="108" t="s">
+      <c r="AD60" s="63" t="s">
         <v>681</v>
       </c>
-      <c r="AD60" s="63" t="s">
+      <c r="AE60" s="63" t="s">
         <v>682</v>
       </c>
-      <c r="AE60" s="63" t="s">
+      <c r="AF60" s="63" t="s">
         <v>683</v>
       </c>
-      <c r="AF60" s="63" t="s">
+      <c r="AG60" s="63" t="s">
         <v>684</v>
-      </c>
-      <c r="AG60" s="63" t="s">
-        <v>685</v>
       </c>
       <c r="AH60" s="63"/>
       <c r="AI60" s="63"/>
       <c r="AJ60" s="63" t="s">
+        <v>685</v>
+      </c>
+      <c r="AK60" s="102" t="s">
         <v>686</v>
-      </c>
-      <c r="AK60" s="102" t="s">
-        <v>687</v>
       </c>
       <c r="AL60" s="63"/>
       <c r="AM60" s="63" t="s">
@@ -9932,13 +10000,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="22" t="s">
+        <v>687</v>
+      </c>
+      <c r="E61" s="22" t="s">
         <v>688</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="F61" s="80" t="s">
         <v>689</v>
-      </c>
-      <c r="F61" s="80" t="s">
-        <v>690</v>
       </c>
       <c r="G61" s="24" t="s">
         <v>154</v>
@@ -9956,7 +10024,7 @@
         <v>483</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M61" s="23" t="s">
         <v>129</v>
@@ -9965,7 +10033,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="P61" s="22">
         <v>6</v>
@@ -9990,28 +10058,28 @@
         <v>50</v>
       </c>
       <c r="AB61" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AC61" s="23"/>
       <c r="AD61" s="23" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE61" s="23" t="s">
         <v>694</v>
       </c>
-      <c r="AE61" s="23" t="s">
+      <c r="AF61" s="23" t="s">
         <v>695</v>
-      </c>
-      <c r="AF61" s="23" t="s">
-        <v>696</v>
       </c>
       <c r="AG61" s="23"/>
       <c r="AH61" s="23"/>
       <c r="AI61" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="AJ61" s="23" t="s">
         <v>697</v>
       </c>
-      <c r="AJ61" s="23" t="s">
+      <c r="AK61" s="101" t="s">
         <v>698</v>
-      </c>
-      <c r="AK61" s="101" t="s">
-        <v>699</v>
       </c>
       <c r="AL61" s="23"/>
       <c r="AM61" s="23" t="s">
@@ -10031,16 +10099,16 @@
         <v>7</v>
       </c>
       <c r="D62" s="46" t="s">
+        <v>699</v>
+      </c>
+      <c r="E62" s="46" t="s">
         <v>700</v>
       </c>
-      <c r="E62" s="46" t="s">
+      <c r="F62" s="108" t="s">
         <v>701</v>
       </c>
-      <c r="F62" s="108" t="s">
+      <c r="G62" s="47" t="s">
         <v>702</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>703</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>126</v>
@@ -10052,10 +10120,10 @@
         <v>68</v>
       </c>
       <c r="K62" s="46" t="s">
+        <v>703</v>
+      </c>
+      <c r="L62" s="46" t="s">
         <v>704</v>
-      </c>
-      <c r="L62" s="46" t="s">
-        <v>705</v>
       </c>
       <c r="M62" s="48" t="s">
         <v>129</v>
@@ -10064,7 +10132,7 @@
         <v>51</v>
       </c>
       <c r="O62" s="46" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="P62" s="57">
         <v>5</v>
@@ -10089,28 +10157,28 @@
         <v>51</v>
       </c>
       <c r="AB62" s="48" t="s">
+        <v>706</v>
+      </c>
+      <c r="AC62" s="90" t="s">
         <v>707</v>
       </c>
-      <c r="AC62" s="90" t="s">
+      <c r="AD62" s="48" t="s">
         <v>708</v>
-      </c>
-      <c r="AD62" s="48" t="s">
-        <v>709</v>
       </c>
       <c r="AE62" s="48" t="s">
         <v>207</v>
       </c>
       <c r="AF62" s="48" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG62" s="48"/>
       <c r="AH62" s="48"/>
       <c r="AI62" s="48"/>
       <c r="AJ62" s="48" t="s">
+        <v>710</v>
+      </c>
+      <c r="AK62" s="99" t="s">
         <v>711</v>
-      </c>
-      <c r="AK62" s="99" t="s">
-        <v>712</v>
       </c>
       <c r="AL62" s="48"/>
       <c r="AM62" s="48" t="s">
@@ -10131,19 +10199,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
+        <v>712</v>
+      </c>
+      <c r="E63" s="22" t="s">
         <v>713</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="F63" s="80" t="s">
         <v>714</v>
       </c>
-      <c r="F63" s="80" t="s">
+      <c r="G63" s="24" t="s">
         <v>715</v>
       </c>
-      <c r="G63" s="24" t="s">
+      <c r="H63" s="23" t="s">
         <v>716</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>717</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>48</v>
@@ -10152,10 +10220,10 @@
         <v>109</v>
       </c>
       <c r="K63" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="L63" s="22" t="s">
         <v>718</v>
-      </c>
-      <c r="L63" s="22" t="s">
-        <v>719</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>62</v>
@@ -10164,7 +10232,7 @@
         <v>50</v>
       </c>
       <c r="O63" s="22" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P63" s="87">
         <v>10</v>
@@ -10189,13 +10257,13 @@
         <v>51</v>
       </c>
       <c r="AB63" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="AC63" s="80" t="s">
         <v>721</v>
       </c>
-      <c r="AC63" s="80" t="s">
+      <c r="AD63" s="23" t="s">
         <v>722</v>
-      </c>
-      <c r="AD63" s="23" t="s">
-        <v>723</v>
       </c>
       <c r="AE63" s="23" t="s">
         <v>207</v>
@@ -10205,10 +10273,10 @@
       <c r="AH63" s="23"/>
       <c r="AI63" s="23"/>
       <c r="AJ63" s="23" t="s">
+        <v>723</v>
+      </c>
+      <c r="AK63" s="101" t="s">
         <v>724</v>
-      </c>
-      <c r="AK63" s="101" t="s">
-        <v>725</v>
       </c>
       <c r="AL63" s="23"/>
       <c r="AM63" s="23" t="s">
@@ -10228,19 +10296,19 @@
         <v>0</v>
       </c>
       <c r="D64" s="61" t="s">
+        <v>725</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="63" t="s">
         <v>726</v>
       </c>
-      <c r="E64" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="63" t="s">
+      <c r="G64" s="64" t="s">
         <v>727</v>
       </c>
-      <c r="G64" s="64" t="s">
-        <v>728</v>
-      </c>
       <c r="H64" s="63" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I64" s="63" t="s">
         <v>48</v>
@@ -10257,7 +10325,7 @@
         <v>48</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P64" s="63">
         <v>2</v>
@@ -10298,10 +10366,10 @@
       <c r="AH64" s="63"/>
       <c r="AI64" s="63"/>
       <c r="AJ64" s="63" t="s">
+        <v>729</v>
+      </c>
+      <c r="AK64" s="102" t="s">
         <v>730</v>
-      </c>
-      <c r="AK64" s="102" t="s">
-        <v>731</v>
       </c>
       <c r="AL64" s="63"/>
       <c r="AM64" s="63" t="s">
@@ -10322,16 +10390,16 @@
         <v>5</v>
       </c>
       <c r="D65" s="37" t="s">
+        <v>731</v>
+      </c>
+      <c r="E65" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="F65" s="40" t="s">
         <v>733</v>
       </c>
-      <c r="F65" s="40" t="s">
+      <c r="G65" s="37" t="s">
         <v>734</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>735</v>
       </c>
       <c r="H65" s="37" t="s">
         <v>310</v>
@@ -10343,10 +10411,10 @@
         <v>80</v>
       </c>
       <c r="K65" s="37" t="s">
+        <v>735</v>
+      </c>
+      <c r="L65" s="37" t="s">
         <v>736</v>
-      </c>
-      <c r="L65" s="37" t="s">
-        <v>737</v>
       </c>
       <c r="M65" s="37" t="s">
         <v>62</v>
@@ -10355,7 +10423,7 @@
         <v>50</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P65" s="37">
         <v>6</v>
@@ -10373,22 +10441,22 @@
         <v>50</v>
       </c>
       <c r="AB65" s="37" t="s">
+        <v>738</v>
+      </c>
+      <c r="AD65" s="40" t="s">
         <v>739</v>
-      </c>
-      <c r="AD65" s="40" t="s">
-        <v>740</v>
       </c>
       <c r="AE65" s="37" t="s">
         <v>451</v>
       </c>
       <c r="AF65" s="37" t="s">
+        <v>740</v>
+      </c>
+      <c r="AJ65" s="37" t="s">
         <v>741</v>
       </c>
-      <c r="AJ65" s="37" t="s">
+      <c r="AK65" s="95" t="s">
         <v>742</v>
-      </c>
-      <c r="AK65" s="95" t="s">
-        <v>743</v>
       </c>
       <c r="AM65" s="23" t="s">
         <v>55</v>
@@ -10403,13 +10471,13 @@
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
+        <v>743</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>744</v>
       </c>
-      <c r="E66" s="37" t="s">
+      <c r="F66" s="37" t="s">
         <v>745</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>746</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>381</v>
@@ -10418,7 +10486,7 @@
         <v>381</v>
       </c>
       <c r="O66" s="37" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="P66" s="37">
         <v>5</v>
@@ -10436,25 +10504,25 @@
         <v>51</v>
       </c>
       <c r="AB66" s="37" t="s">
+        <v>747</v>
+      </c>
+      <c r="AC66" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD66" s="37" t="s">
         <v>748</v>
       </c>
-      <c r="AC66" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD66" s="37" t="s">
+      <c r="AE66" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="AE66" s="37" t="s">
+      <c r="AJ66" s="37" t="s">
         <v>750</v>
       </c>
-      <c r="AJ66" s="37" t="s">
+      <c r="AK66" s="95" t="s">
         <v>751</v>
       </c>
-      <c r="AK66" s="95" t="s">
+      <c r="AM66" s="37" t="s">
         <v>752</v>
-      </c>
-      <c r="AM66" s="37" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="67" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10465,22 +10533,22 @@
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
+        <v>753</v>
+      </c>
+      <c r="E67" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="E67" s="37" t="s">
+      <c r="F67" s="37" t="s">
         <v>755</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="G67" s="37" t="s">
         <v>756</v>
       </c>
-      <c r="G67" s="37" t="s">
+      <c r="H67" s="37" t="s">
+        <v>756</v>
+      </c>
+      <c r="O67" s="37" t="s">
         <v>757</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>757</v>
-      </c>
-      <c r="O67" s="37" t="s">
-        <v>758</v>
       </c>
       <c r="P67" s="28">
         <v>5</v>
@@ -10498,13 +10566,13 @@
         <v>51</v>
       </c>
       <c r="AB67" s="37" t="s">
+        <v>758</v>
+      </c>
+      <c r="AJ67" s="37" t="s">
         <v>759</v>
       </c>
-      <c r="AJ67" s="37" t="s">
+      <c r="AK67" s="95" t="s">
         <v>760</v>
-      </c>
-      <c r="AK67" s="95" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="68" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -10515,13 +10583,13 @@
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
+        <v>761</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="F68" s="37" t="s">
         <v>763</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>764</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>381</v>
@@ -10530,7 +10598,7 @@
         <v>381</v>
       </c>
       <c r="O68" s="37" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P68" s="28">
         <v>5</v>
@@ -10548,13 +10616,13 @@
         <v>51</v>
       </c>
       <c r="AB68" s="37" t="s">
+        <v>765</v>
+      </c>
+      <c r="AJ68" s="37" t="s">
         <v>766</v>
       </c>
-      <c r="AJ68" s="37" t="s">
+      <c r="AK68" s="95" t="s">
         <v>767</v>
-      </c>
-      <c r="AK68" s="95" t="s">
-        <v>768</v>
       </c>
       <c r="AO68" s="2"/>
     </row>
@@ -10566,22 +10634,22 @@
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
+        <v>768</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>769</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="F69" s="37" t="s">
         <v>770</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>771</v>
       </c>
       <c r="G69" s="37" t="s">
         <v>297</v>
       </c>
       <c r="I69" s="37" t="s">
+        <v>771</v>
+      </c>
+      <c r="O69" s="37" t="s">
         <v>772</v>
-      </c>
-      <c r="O69" s="37" t="s">
-        <v>773</v>
       </c>
       <c r="P69" s="28">
         <v>5</v>
@@ -10599,19 +10667,19 @@
         <v>51</v>
       </c>
       <c r="AB69" s="37" t="s">
+        <v>773</v>
+      </c>
+      <c r="AJ69" s="37" t="s">
         <v>774</v>
       </c>
-      <c r="AJ69" s="37" t="s">
+      <c r="AK69" s="95" t="s">
         <v>775</v>
       </c>
-      <c r="AK69" s="95" t="s">
+      <c r="AM69" s="37" t="s">
         <v>776</v>
       </c>
-      <c r="AM69" s="37" t="s">
+      <c r="AN69" s="37" t="s">
         <v>777</v>
-      </c>
-      <c r="AN69" s="37" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="70" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10622,13 +10690,13 @@
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
+        <v>778</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>779</v>
       </c>
-      <c r="E70" s="37" t="s">
+      <c r="F70" s="92" t="s">
         <v>780</v>
-      </c>
-      <c r="F70" s="92" t="s">
-        <v>781</v>
       </c>
       <c r="G70" s="37" t="s">
         <v>381</v>
@@ -10637,7 +10705,7 @@
         <v>381</v>
       </c>
       <c r="O70" s="37" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P70" s="28">
         <v>4</v>
@@ -10655,40 +10723,55 @@
         <v>51</v>
       </c>
       <c r="AB70" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AJ70" s="37" t="s">
         <v>783</v>
       </c>
-      <c r="AJ70" s="37" t="s">
+      <c r="AK70" s="95" t="s">
         <v>784</v>
-      </c>
-      <c r="AK70" s="95" t="s">
-        <v>785</v>
       </c>
       <c r="AP70"/>
     </row>
     <row r="71" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79" t="s">
-        <v>377</v>
+        <v>62</v>
       </c>
       <c r="B71" s="37">
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
+        <v>785</v>
+      </c>
+      <c r="E71" s="37" t="s">
         <v>786</v>
       </c>
-      <c r="E71" s="37" t="s">
+      <c r="F71" s="109" t="s">
+        <v>846</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="J71" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="K71" s="49" t="s">
+        <v>416</v>
+      </c>
+      <c r="L71" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="M71" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="N71" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="O71" s="37" t="s">
         <v>787</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>788</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="O71" s="37" t="s">
-        <v>789</v>
       </c>
       <c r="P71" s="28">
         <v>7</v>
@@ -10706,22 +10789,22 @@
         <v>51</v>
       </c>
       <c r="AB71" s="37" t="s">
+        <v>788</v>
+      </c>
+      <c r="AE71" s="37" t="s">
+        <v>789</v>
+      </c>
+      <c r="AJ71" s="37" t="s">
         <v>790</v>
       </c>
-      <c r="AE71" s="37" t="s">
+      <c r="AK71" s="95" t="s">
         <v>791</v>
       </c>
-      <c r="AJ71" s="37" t="s">
+      <c r="AM71" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="AN71" s="37" t="s">
         <v>792</v>
-      </c>
-      <c r="AK71" s="95" t="s">
-        <v>793</v>
-      </c>
-      <c r="AM71" s="37" t="s">
-        <v>753</v>
-      </c>
-      <c r="AN71" s="37" t="s">
-        <v>794</v>
       </c>
       <c r="AP71"/>
     </row>
@@ -10736,19 +10819,19 @@
         <v>0</v>
       </c>
       <c r="D72" s="63" t="s">
+        <v>793</v>
+      </c>
+      <c r="E72" s="63" t="s">
+        <v>794</v>
+      </c>
+      <c r="F72" s="76" t="s">
         <v>795</v>
       </c>
-      <c r="E72" s="63" t="s">
+      <c r="G72" s="63" t="s">
         <v>796</v>
       </c>
-      <c r="F72" s="76" t="s">
-        <v>797</v>
-      </c>
-      <c r="G72" s="63" t="s">
-        <v>798</v>
-      </c>
       <c r="H72" s="63" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="I72" s="63" t="s">
         <v>48</v>
@@ -10765,7 +10848,7 @@
         <v>48</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="P72" s="65">
         <v>6</v>
@@ -10808,10 +10891,10 @@
       <c r="AH72" s="63"/>
       <c r="AI72" s="63"/>
       <c r="AJ72" s="63" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="AK72" s="102" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AL72" s="63"/>
       <c r="AM72" s="63" t="s">
@@ -10829,22 +10912,22 @@
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
+        <v>800</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>801</v>
+      </c>
+      <c r="F73" s="80" t="s">
         <v>802</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="G73" s="37" t="s">
         <v>803</v>
       </c>
-      <c r="F73" s="80" t="s">
+      <c r="H73" s="37" t="s">
+        <v>803</v>
+      </c>
+      <c r="O73" s="37" t="s">
         <v>804</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>805</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>805</v>
-      </c>
-      <c r="O73" s="37" t="s">
-        <v>806</v>
       </c>
       <c r="P73" s="28">
         <v>6</v>
@@ -10862,13 +10945,13 @@
         <v>51</v>
       </c>
       <c r="AB73" s="37" t="s">
+        <v>805</v>
+      </c>
+      <c r="AJ73" s="37" t="s">
+        <v>806</v>
+      </c>
+      <c r="AK73" s="95" t="s">
         <v>807</v>
-      </c>
-      <c r="AJ73" s="37" t="s">
-        <v>808</v>
-      </c>
-      <c r="AK73" s="95" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="74" spans="1:42" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -10879,16 +10962,16 @@
         <v>2026</v>
       </c>
       <c r="D74" t="s">
+        <v>808</v>
+      </c>
+      <c r="E74" t="s">
+        <v>809</v>
+      </c>
+      <c r="F74" s="92" t="s">
         <v>810</v>
       </c>
-      <c r="E74" t="s">
+      <c r="O74" t="s">
         <v>811</v>
-      </c>
-      <c r="F74" s="92" t="s">
-        <v>812</v>
-      </c>
-      <c r="O74" t="s">
-        <v>813</v>
       </c>
       <c r="P74">
         <v>6</v>
@@ -10911,19 +10994,19 @@
         <v>51</v>
       </c>
       <c r="AB74" t="s">
+        <v>812</v>
+      </c>
+      <c r="AE74" s="37" t="s">
+        <v>813</v>
+      </c>
+      <c r="AF74" s="37" t="s">
         <v>814</v>
       </c>
-      <c r="AE74" s="37" t="s">
+      <c r="AJ74" t="s">
         <v>815</v>
       </c>
-      <c r="AF74" s="37" t="s">
+      <c r="AK74" s="103" t="s">
         <v>816</v>
-      </c>
-      <c r="AJ74" t="s">
-        <v>817</v>
-      </c>
-      <c r="AK74" s="103" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="75" spans="1:42" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -10934,34 +11017,34 @@
         <v>2026</v>
       </c>
       <c r="D75" s="37" t="s">
+        <v>817</v>
+      </c>
+      <c r="E75" t="s">
+        <v>818</v>
+      </c>
+      <c r="F75" s="92" t="s">
         <v>819</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" s="37" t="s">
         <v>820</v>
       </c>
-      <c r="F75" s="92" t="s">
+      <c r="H75" s="37" t="s">
         <v>821</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>822</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>823</v>
       </c>
       <c r="J75" s="37" t="s">
         <v>68</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="L75" s="37" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="M75" s="37" t="s">
         <v>62</v>
       </c>
       <c r="O75" s="37" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="P75" s="28">
         <v>6</v>
@@ -10979,22 +11062,22 @@
         <v>51</v>
       </c>
       <c r="AC75" s="92" t="s">
+        <v>825</v>
+      </c>
+      <c r="AD75" s="92" t="s">
+        <v>826</v>
+      </c>
+      <c r="AE75" s="37" t="s">
         <v>827</v>
       </c>
-      <c r="AD75" s="92" t="s">
+      <c r="AK75" s="95" t="s">
         <v>828</v>
-      </c>
-      <c r="AE75" s="37" t="s">
-        <v>829</v>
-      </c>
-      <c r="AK75" s="95" t="s">
-        <v>830</v>
       </c>
       <c r="AM75" s="37" t="s">
         <v>55</v>
       </c>
       <c r="AN75" s="37" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AP75"/>
     </row>
@@ -11006,10 +11089,10 @@
         <v>2026</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G76" s="37" t="s">
         <v>143</v>
@@ -11036,7 +11119,7 @@
         <v>51</v>
       </c>
       <c r="O76" s="37" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="P76" s="28">
         <v>4</v>
@@ -11048,13 +11131,13 @@
         <v>51</v>
       </c>
       <c r="AC76" s="92" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AE76" s="37" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="AF76" s="92" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="AM76" s="37" t="s">
         <v>55</v>
@@ -11068,13 +11151,13 @@
         <v>2026</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="E77" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="F77" s="92" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="G77" s="37" t="s">
         <v>381</v>
@@ -11083,7 +11166,7 @@
         <v>381</v>
       </c>
       <c r="O77" s="37" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="P77" s="28">
         <v>6</v>
@@ -11098,22 +11181,22 @@
         <v>0</v>
       </c>
       <c r="AB77" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="AE77" s="37" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AJ77" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="AK77" s="95" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="AM77" s="37" t="s">
         <v>196</v>
       </c>
       <c r="AP77" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="78" spans="1:42" ht="102" x14ac:dyDescent="0.2">
@@ -11124,7 +11207,7 @@
         <v>2026</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="G78" s="37" t="s">
         <v>381</v>
@@ -11133,7 +11216,7 @@
         <v>381</v>
       </c>
       <c r="O78" s="37" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="P78" s="28">
         <v>5</v>
@@ -11145,14 +11228,82 @@
         <v>51</v>
       </c>
       <c r="AB78" s="37" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="AE78" s="37" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="B79" s="37"/>
+        <v>813</v>
+      </c>
+    </row>
+    <row r="79" spans="1:42" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A79" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="37">
+        <v>2026</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>849</v>
+      </c>
+      <c r="F79" s="92" t="s">
+        <v>850</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>851</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>852</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K79" s="49" t="s">
+        <v>853</v>
+      </c>
+      <c r="L79" s="37" t="s">
+        <v>854</v>
+      </c>
+      <c r="M79" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="N79" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="O79" s="37" t="s">
+        <v>855</v>
+      </c>
+      <c r="P79" s="28">
+        <v>6</v>
+      </c>
+      <c r="Q79" s="28">
+        <v>5</v>
+      </c>
+      <c r="R79" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="S79" s="28">
+        <v>2</v>
+      </c>
+      <c r="AB79" s="37" t="s">
+        <v>856</v>
+      </c>
+      <c r="AD79" s="37" t="s">
+        <v>857</v>
+      </c>
+      <c r="AE79" s="37" t="s">
+        <v>859</v>
+      </c>
+      <c r="AJ79" s="37" t="s">
+        <v>860</v>
+      </c>
+      <c r="AK79" s="95" t="s">
+        <v>861</v>
+      </c>
+      <c r="AM79" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="AO79" s="37" t="s">
+        <v>858</v>
+      </c>
     </row>
     <row r="80" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B80" s="37"/>
@@ -13765,11 +13916,7 @@
       <c r="B949" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP76" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP76">
-      <sortCondition ref="B1:B76"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AP1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
@@ -13914,6 +14061,8 @@
     <hyperlink ref="F77" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
     <hyperlink ref="AF76" r:id="rId96" display="https://lnkd.in/p/eS8dQ3fZ" xr:uid="{0B677043-826E-834D-868D-4B423761D01A}"/>
     <hyperlink ref="AC76" r:id="rId97" xr:uid="{3EDB0987-2302-D449-AB7F-B05F134CEDA6}"/>
+    <hyperlink ref="F71" r:id="rId98" xr:uid="{F334CBC2-D676-7F4F-875E-6623C7C54EDA}"/>
+    <hyperlink ref="F79" r:id="rId99" xr:uid="{8440A738-A599-D548-AD62-6630D8D2835B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Library/CloudStorage/OneDrive-UniversidadPolitécnicadeMadrid/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375846A0-4FB5-7649-B7B2-3D8ED3FB6C80}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C88F85C-B454-4740-9C84-47D987D1871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AP$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="869">
   <si>
     <t>Tipo</t>
   </si>
@@ -704,6 +691,9 @@
 }</t>
   </si>
   <si>
+    <t>Preprint</t>
+  </si>
+  <si>
     <t>Is ChatGPT capable of solving classical Communications and Networking problems?</t>
   </si>
   <si>
@@ -771,7 +761,7 @@
     <t>[http://ufldl.stanford.edu/housenumbers/, https://github.com/zalandoresearch/fashion-mnist, https://www.cs.toronto.edu/~kriz/cifar.html, https://zenodo.org/records/18805665, https://github.com/javicond3/Adaptive-Resolution-Inference_ARI]</t>
   </si>
   <si>
-    <t>[FUN4DATE, SMARTY]</t>
+    <t>[FUN4DATE]</t>
   </si>
   <si>
     <t xml:space="preserve">[https://x.com/HPCPapers/status/1828674673246081463?s=20, https://scispace.com/papers/adaptive-resolution-inference-ari-energy-efficient-machine-yka3u8nny0] </t>
@@ -883,9 +873,6 @@
     <t>[https://edatos.consorciomadrono.es/dataset.xhtml?persistentId=doi:10.21950/L7VJZV, https://github.com/ging/escapp, ]</t>
   </si>
   <si>
-    <t>[FUN4DATE]</t>
-  </si>
-  <si>
     <t>[https://innovacioneducativa.upm.es/articulos/empowering-database-learning-through-remote-educational-escape-rooms?utm_source=chatgpt.com, https://cyberaula.github.io/research, https://x.com/WGOV/status/1835538317942706214?s=20]</t>
   </si>
   <si>
@@ -941,6 +928,9 @@
     <t>[https://doi.org/10.5281/zenodo.14173285]</t>
   </si>
   <si>
+    <t>[FUN4DATE, SMARTY]</t>
+  </si>
+  <si>
     <t>[https://www.linkedin.com/posts/javier-conde-diaz_enhanced-fiware-based-architecture-for-cyberphysical-activity-7264301875078852611-sux-, https://github.com/gauravfs-14/awesome-tinyml]</t>
   </si>
   <si>
@@ -1391,9 +1381,6 @@
     <t>Integrating Artificial Intelligence in Higher Education: Potential, Challenges and Opportunities</t>
   </si>
   <si>
-    <t>blknAaTinKkC</t>
-  </si>
-  <si>
     <t>https://oa.upm.es/85213/</t>
   </si>
   <si>
@@ -1413,9 +1400,6 @@
   publisher = {Universidad Politécnica de Madrid},
   url = {https://oa.upm.es/85213/},
 }</t>
-  </si>
-  <si>
-    <t>Preprint</t>
   </si>
   <si>
     <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
@@ -2375,9 +2359,6 @@
     <t>Inteligencia Artificial en la Educación Superior 2025: Transformaciones Docentes, Herramientas y Buenas Prácticas</t>
   </si>
   <si>
-    <t>yD5IFk8b50cC</t>
-  </si>
-  <si>
     <t>https://doi.org/10.20868/UPM.book.91489</t>
   </si>
   <si>
@@ -2403,9 +2384,6 @@
     <t>Uso ético y responsable de la Inteligencia Artificial en la educación: Guía Buenas Prácticas</t>
   </si>
   <si>
-    <t>rO6llkc54NcC</t>
-  </si>
-  <si>
     <t>https://oa.upm.es/91518/</t>
   </si>
   <si>
@@ -2520,6 +2498,9 @@
   </si>
   <si>
     <t>[FUN4DATE, BRIDGE-AI, TUCAN6-CM]</t>
+  </si>
+  <si>
+    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/, https://www.linkedin.com/posts/javier-conde-diaz_upm-ngsi-rag-activity-7503435475433545728-YfYa?utm_source=social_share_send&amp;utm_medium=android_app&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
   </si>
   <si>
     <t>The proliferation of Generative Artificial Ingelligence (AI), especially Large Language Models, presents transformative opportunities for urban applications through Urban Foundation Models. However, base models face limitations, as they only contain the knowledge available at the time of training, and updating them is both time-consuming and costly. Retrieval Augmented Generation (RAG) has emerged in the literature as the preferred approach for injecting contextual information into Foundation Models. It prevails over techniques such as fine-tuning, which are less effective in dynamic, real-time scenarios like those found in urban environments. However, traditional RAG architectures, based on semantic databases, knowledge graphs, structured data, or AI-powered web searches, do not fully meet the demands of urban contexts. Urban environments are complex systems characterized by large volumes of interconnected data, frequent updates, real-time processing requirements, security needs, and strong links to the physical world. This work proposes a real-time spatial RAG architecture that defines the necessary components for the effective integration of generative AI into cities, leveraging temporal and spatial filtering capabilities through linked data. The proposed architecture is implemented using FIWARE, an ecosystem of software components to develop smart city solutions and digital twins. The design and implementation are demonstrated through the use case of a tourism assistant in the city of Madrid. The use case serves to validate the correct integration of Foundation Models through the proposed RAG architecture.</t>
@@ -2971,6 +2952,9 @@
     <t>4OULZ7Gr8RgC</t>
   </si>
   <si>
+    <t>https://doi.org/10.1109/TC.2026.3732142</t>
+  </si>
+  <si>
     <t>T. Fu, G. Martínez, J. Conde, C. Arriaga, P. Reviriego, X. Qi, S. Liu</t>
   </si>
   <si>
@@ -3130,10 +3114,25 @@
     <t>AI agents for scaling real-time support in educational escape rooms</t>
   </si>
   <si>
+    <t>SP6oXDckpogC</t>
+  </si>
+  <si>
     <t>10.1109/MITP.2026.3712183</t>
   </si>
   <si>
     <t>E. Barra, S. López-Pernas, J. Conde, A. Gordillo</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/97555/</t>
+  </si>
+  <si>
+    <t>FUN4DATE, ENDGAME, IGLUE</t>
+  </si>
+  <si>
+    <t>[https://lnkd.in/p/eS8dQ3fZ,]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
   </si>
   <si>
     <t>KxtntwgDAa4C</t>
@@ -3162,34 +3161,34 @@
 }</t>
   </si>
   <si>
-    <t>cowork_2026-08-10: Id_google_scholar añadido -&gt; KxtntwgDAa4C; Citas GS vacio -&gt; 0; Open Access anadido (arXiv); Sumary (abstract) anadido desde Google Scholar</t>
-  </si>
-  <si>
     <t>Decoding-Level Taboo: A Diagnostic Stress Test for LLM Robustness</t>
   </si>
   <si>
+    <t>UxriW0iASnsC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2608.09900</t>
+  </si>
+  <si>
     <t>T. Chuyo Kamijo, O. Rottenstreich, J. Conde, G. Martínez, P. Reviriego</t>
   </si>
   <si>
     <t>[https://arxiv.org/abs/2608.09900, https://huggingface.co/papers/2608.09900]</t>
   </si>
   <si>
-    <t>[https://lnkd.in/p/eS8dQ3fZ,]</t>
-  </si>
-  <si>
-    <t>FUN4DATE, ENDGAME, IGLUE</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/97555/</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TC.2026.3732142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
-  </si>
-  <si>
-    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/, https://www.linkedin.com/posts/javier-conde-diaz_upm-ngsi-rag-activity-7503435475433545728-YfYa?utm_source=social_share_send&amp;utm_medium=android_app&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+    <t>Large language model evaluations typically focus on performance under nominal conditions, creating an illusion of capability where models comfortably walk a narrow, highly optimized generation corridor. In real-world deployments, however, complex system prompts, safety guardrails, and structural constraints continuously force models off this nominal path, driving a divergence between benchmark scores and deployment performance. To address this issue, we introduce Decoding-Level Taboo, a zero-prompt diagnostic stress test that intervenes directly in logit space at runtime, forcing models out of their nominal paths. By dynamically masking primary candidate tokens at word boundaries, Taboo forces machine circumlocution. Evaluating Taboo across several open-weight model families reveals that off-path robustness is heavily influenced by both parameter scale and post-training instruction alignment, with robustness generally improving with model size and alignment. Beyond the results presented in this paper, Taboo provides a novel primitive for generating diverse synthetic datasets, stress-testing runtime safety guardrails, and auditing model reliability prior to real-world deployment.</t>
+  </si>
+  <si>
+    <t>@misc{kamijo2026decoding,
+  title = {Decoding-Level Taboo: A Diagnostic Stress Test for LLM Robustness},
+  author = {Kamijo, Tadanobu Chuyo and Rottenstreich, Ori and Conde, Javier and Mart\'inez, Gonzalo and Reviriego, Pedro},
+  year = {2026},
+  eprint = {2608.09900},
+  archivePrefix = {arXiv},
+  primaryClass = {cs.CL},
+  doi = {10.48550/arXiv.2608.09900},
+  url = {https://doi.org/10.48550/arXiv.2608.09900}
+}</t>
   </si>
   <si>
     <t>Evaluating large language models with tests of Spanish as a foreign language: pass or fail?</t>
@@ -3217,9 +3216,6 @@
   </si>
   <si>
     <t>[https://zenodo.org/doi/10.5281/zenodo.13643393]</t>
-  </si>
-  <si>
-    <t>Subirlo a archivo digital upm</t>
   </si>
   <si>
     <t>FUN4DATE, SMARTY</t>
@@ -3240,6 +3236,27 @@
     url = {https://doi.org/10.1093/applin/amag048},
     eprint = {https://academic.oup.com/applij/advance-article-pdf/doi/10.1093/applin/amag048/71017839/amag048.pdf},
 }</t>
+  </si>
+  <si>
+    <t>Subirlo a archivo digital upm</t>
+  </si>
+  <si>
+    <t>Dependability and Error Detection for the Stable Diffusion Generative Model</t>
+  </si>
+  <si>
+    <t>IEEE Transactions on Reliability</t>
+  </si>
+  <si>
+    <t>doi.org/10.1109/TR.2026.3734708</t>
+  </si>
+  <si>
+    <t>Índice de Impacto JCR (2025): 5.4 (18/128 - Q1)</t>
+  </si>
+  <si>
+    <t>Computer Sicence, Software Engineering</t>
+  </si>
+  <si>
+    <t>Z. Gao, L. Yuan, J. Conde, P. Reviriego, Á. Alonso, S. Liu, F. Lombardi</t>
   </si>
 </sst>
 </file>
@@ -3471,7 +3488,7 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3790,7 +3807,7 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
@@ -4182,8 +4199,8 @@
     <col min="40" max="40" width="48.5" style="37" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="48.5" style="37" customWidth="1"/>
     <col min="42" max="42" width="99.1640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="8.83203125" style="1" customWidth="1"/>
-    <col min="47" max="16384" width="8.83203125" style="1"/>
+    <col min="43" max="47" width="8.83203125" style="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4558,7 +4575,7 @@
         <v>50</v>
       </c>
       <c r="S4" s="19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T4" s="19"/>
       <c r="U4" s="20"/>
@@ -4658,7 +4675,7 @@
         <v>50</v>
       </c>
       <c r="S5" s="52">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T5" s="52"/>
       <c r="U5" s="70"/>
@@ -4946,7 +4963,7 @@
         <v>51</v>
       </c>
       <c r="S8" s="58">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="T8" s="58">
         <v>63</v>
@@ -5064,7 +5081,7 @@
         <v>50</v>
       </c>
       <c r="S9" s="58">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="T9" s="58">
         <v>107</v>
@@ -5180,7 +5197,7 @@
         <v>50</v>
       </c>
       <c r="S10" s="27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T10" s="27"/>
       <c r="U10" s="33"/>
@@ -5600,26 +5617,26 @@
     </row>
     <row r="15" spans="1:42" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="78" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="B15" s="82">
         <v>2023</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E15" s="61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G15" s="61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I15" s="64" t="s">
         <v>48</v>
@@ -5636,7 +5653,7 @@
         <v>48</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P15" s="63">
         <v>4</v>
@@ -5661,7 +5678,7 @@
         <v>51</v>
       </c>
       <c r="AB15" s="63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="63" t="s">
         <v>48</v>
@@ -5679,14 +5696,14 @@
       <c r="AH15" s="63"/>
       <c r="AI15" s="63"/>
       <c r="AJ15" s="63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AK15" s="102" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AL15" s="63"/>
       <c r="AM15" s="63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AN15" s="63"/>
       <c r="AO15" s="63"/>
@@ -5703,16 +5720,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>126</v>
@@ -5724,10 +5741,10 @@
         <v>109</v>
       </c>
       <c r="K16" s="49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M16" s="49" t="s">
         <v>62</v>
@@ -5736,7 +5753,7 @@
         <v>50</v>
       </c>
       <c r="O16" s="49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P16" s="49">
         <v>6</v>
@@ -5748,7 +5765,7 @@
         <v>51</v>
       </c>
       <c r="S16" s="67">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" s="67">
         <v>1</v>
@@ -5765,32 +5782,32 @@
         <v>50</v>
       </c>
       <c r="AB16" s="49" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC16" s="56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AD16" s="49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AE16" s="49" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="AF16" s="49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG16" s="63"/>
       <c r="AH16" s="49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI16" s="49" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AJ16" s="63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AK16" s="102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL16" s="63"/>
       <c r="AM16" s="57" t="s">
@@ -5811,19 +5828,19 @@
         <v>8.5</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I17" s="49" t="s">
         <v>48</v>
@@ -5832,10 +5849,10 @@
         <v>109</v>
       </c>
       <c r="K17" s="49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M17" s="49" t="s">
         <v>62</v>
@@ -5844,7 +5861,7 @@
         <v>13</v>
       </c>
       <c r="O17" s="49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P17" s="49">
         <v>4</v>
@@ -5853,13 +5870,13 @@
         <v>2</v>
       </c>
       <c r="R17" s="49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S17" s="67">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="T17" s="69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="U17" s="67">
         <v>15</v>
@@ -5873,30 +5890,30 @@
         <v>51</v>
       </c>
       <c r="AB17" s="49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AC17" s="56" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AD17" s="49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AE17" s="49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF17" s="49" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG17" s="63"/>
       <c r="AH17" s="63"/>
       <c r="AI17" s="49" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AJ17" s="63" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK17" s="102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL17" s="63"/>
       <c r="AM17" s="57" t="s">
@@ -5917,13 +5934,13 @@
         <v>8</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G18" s="49" t="s">
         <v>125</v>
@@ -5938,7 +5955,7 @@
         <v>109</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L18" s="49" t="s">
         <v>128</v>
@@ -5950,7 +5967,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P18" s="49">
         <v>6</v>
@@ -5962,7 +5979,7 @@
         <v>50</v>
       </c>
       <c r="S18" s="67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T18" s="67">
         <v>3</v>
@@ -5979,16 +5996,16 @@
         <v>51</v>
       </c>
       <c r="AB18" s="49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC18" s="56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AD18" s="49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AE18" s="49" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="AF18" s="49" t="s">
         <v>239</v>
@@ -6070,7 +6087,7 @@
         <v>50</v>
       </c>
       <c r="S19" s="67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T19" s="67">
         <v>3</v>
@@ -6096,21 +6113,21 @@
         <v>253</v>
       </c>
       <c r="AE19" s="49" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF19" s="49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG19" s="63"/>
       <c r="AH19" s="63"/>
       <c r="AI19" s="49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AJ19" s="63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AK19" s="102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL19" s="63"/>
       <c r="AM19" s="57" t="s">
@@ -6131,16 +6148,16 @@
         <v>6</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H20" s="25" t="s">
         <v>126</v>
@@ -6152,10 +6169,10 @@
         <v>68</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M20" s="25" t="s">
         <v>129</v>
@@ -6164,7 +6181,7 @@
         <v>50</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P20" s="22">
         <v>6</v>
@@ -6176,10 +6193,10 @@
         <v>51</v>
       </c>
       <c r="S20" s="44">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T20" s="44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U20" s="39"/>
       <c r="V20" s="39"/>
@@ -6191,26 +6208,26 @@
         <v>51</v>
       </c>
       <c r="AB20" s="37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AC20" s="80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AD20" s="37"/>
       <c r="AE20" s="37" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF20" s="37"/>
       <c r="AG20" s="37"/>
       <c r="AH20" s="37"/>
       <c r="AI20" s="25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AJ20" s="37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AK20" s="95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL20" s="37"/>
       <c r="AM20" s="31" t="s">
@@ -6231,13 +6248,13 @@
         <v>4</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G21" s="24" t="s">
         <v>154</v>
@@ -6252,10 +6269,10 @@
         <v>68</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M21" s="23" t="s">
         <v>129</v>
@@ -6264,7 +6281,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P21" s="26">
         <v>6</v>
@@ -6276,7 +6293,7 @@
         <v>51</v>
       </c>
       <c r="S21" s="27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T21" s="27"/>
       <c r="U21" s="33"/>
@@ -6289,24 +6306,24 @@
         <v>50</v>
       </c>
       <c r="AB21" s="23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AC21" s="80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AD21" s="23"/>
       <c r="AE21" s="23" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="AF21" s="23"/>
       <c r="AG21" s="23"/>
       <c r="AH21" s="23"/>
       <c r="AI21" s="23"/>
       <c r="AJ21" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AK21" s="101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL21" s="23"/>
       <c r="AM21" s="31" t="s">
@@ -6327,19 +6344,19 @@
         <v>3</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I22" s="23" t="s">
         <v>48</v>
@@ -6348,10 +6365,10 @@
         <v>68</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M22" s="23" t="s">
         <v>62</v>
@@ -6360,7 +6377,7 @@
         <v>50</v>
       </c>
       <c r="O22" s="22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P22" s="22">
         <v>7</v>
@@ -6372,7 +6389,7 @@
         <v>51</v>
       </c>
       <c r="S22" s="27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" s="27"/>
       <c r="U22" s="33"/>
@@ -6385,26 +6402,26 @@
         <v>51</v>
       </c>
       <c r="AB22" s="23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC22" s="23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AD22" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AE22" s="23" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AF22" s="23"/>
       <c r="AG22" s="23"/>
       <c r="AH22" s="23"/>
       <c r="AI22" s="23"/>
       <c r="AJ22" s="23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK22" s="101" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL22" s="23"/>
       <c r="AM22" s="31" t="s">
@@ -6425,19 +6442,19 @@
         <v>0</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F23" s="80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I23" s="23" t="s">
         <v>48</v>
@@ -6446,10 +6463,10 @@
         <v>68</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>62</v>
@@ -6458,7 +6475,7 @@
         <v>50</v>
       </c>
       <c r="O23" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P23" s="22">
         <v>8</v>
@@ -6483,26 +6500,26 @@
         <v>51</v>
       </c>
       <c r="AB23" s="23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC23" s="23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AD23" s="23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AE23" s="23" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
       <c r="AI23" s="23"/>
       <c r="AJ23" s="23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AK23" s="101" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL23" s="23"/>
       <c r="AM23" s="31" t="s">
@@ -6521,22 +6538,22 @@
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="61" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J24" s="63" t="s">
         <v>48</v>
@@ -6550,7 +6567,7 @@
         <v>48</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P24" s="63">
         <v>5</v>
@@ -6575,10 +6592,10 @@
         <v>51</v>
       </c>
       <c r="AB24" s="63" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC24" s="63" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD24" s="63" t="s">
         <v>48</v>
@@ -6593,10 +6610,10 @@
       <c r="AH24" s="63"/>
       <c r="AI24" s="63"/>
       <c r="AJ24" s="63" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK24" s="102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL24" s="63"/>
       <c r="AM24" s="63" t="s">
@@ -6615,25 +6632,25 @@
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="61" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F25" s="71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G25" s="61" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I25" s="64" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J25" s="63" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K25" s="63"/>
       <c r="L25" s="63"/>
@@ -6644,7 +6661,7 @@
         <v>48</v>
       </c>
       <c r="O25" s="61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P25" s="63">
         <v>4</v>
@@ -6669,16 +6686,16 @@
         <v>51</v>
       </c>
       <c r="AB25" s="63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AC25" s="76" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AD25" s="63" t="s">
         <v>48</v>
       </c>
       <c r="AE25" s="63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AF25" s="63" t="s">
         <v>48</v>
@@ -6687,10 +6704,10 @@
       <c r="AH25" s="63"/>
       <c r="AI25" s="63"/>
       <c r="AJ25" s="63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK25" s="102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL25" s="63"/>
       <c r="AM25" s="48" t="s">
@@ -6709,25 +6726,25 @@
       </c>
       <c r="C26" s="28"/>
       <c r="D26" s="61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E26" s="61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G26" s="61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H26" s="63" t="s">
         <v>126</v>
       </c>
       <c r="I26" s="64" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J26" s="63" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K26" s="63"/>
       <c r="L26" s="63"/>
@@ -6738,7 +6755,7 @@
         <v>48</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P26" s="63">
         <v>4</v>
@@ -6766,7 +6783,7 @@
         <v>48</v>
       </c>
       <c r="AC26" s="76" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AD26" s="63" t="s">
         <v>48</v>
@@ -6781,10 +6798,10 @@
       <c r="AH26" s="63"/>
       <c r="AI26" s="63"/>
       <c r="AJ26" s="63" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AK26" s="102" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL26" s="63"/>
       <c r="AM26" s="48" t="s">
@@ -6803,22 +6820,22 @@
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="61" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I27" s="64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J27" s="63" t="s">
         <v>48</v>
@@ -6832,7 +6849,7 @@
         <v>48</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P27" s="63">
         <v>5</v>
@@ -6857,7 +6874,7 @@
         <v>51</v>
       </c>
       <c r="AB27" s="63" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AC27" s="63" t="s">
         <v>48</v>
@@ -6869,16 +6886,16 @@
         <v>48</v>
       </c>
       <c r="AF27" s="63" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG27" s="63"/>
       <c r="AH27" s="63"/>
       <c r="AI27" s="63"/>
       <c r="AJ27" s="63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AK27" s="102" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL27" s="63"/>
       <c r="AM27" s="63" t="s">
@@ -6890,20 +6907,20 @@
     </row>
     <row r="28" spans="1:42" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B28" s="82">
         <v>2024</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E28" s="61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F28" s="62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G28" s="64" t="s">
         <v>108</v>
@@ -6926,7 +6943,7 @@
         <v>48</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P28" s="63">
         <v>6</v>
@@ -6969,10 +6986,10 @@
       <c r="AH28" s="63"/>
       <c r="AI28" s="63"/>
       <c r="AJ28" s="63" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK28" s="102" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL28" s="63"/>
       <c r="AM28" s="63" t="s">
@@ -6984,26 +7001,26 @@
     </row>
     <row r="29" spans="1:42" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B29" s="82">
         <v>2024</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="61" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E29" s="61" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G29" s="64" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H29" s="63" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I29" s="63" t="s">
         <v>48</v>
@@ -7020,7 +7037,7 @@
         <v>48</v>
       </c>
       <c r="O29" s="63" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P29" s="63">
         <v>4</v>
@@ -7032,7 +7049,7 @@
         <v>51</v>
       </c>
       <c r="S29" s="65">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T29" s="65"/>
       <c r="U29" s="66"/>
@@ -7045,7 +7062,7 @@
         <v>51</v>
       </c>
       <c r="AB29" s="63" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AC29" s="63" t="s">
         <v>48</v>
@@ -7063,10 +7080,10 @@
       <c r="AH29" s="63"/>
       <c r="AI29" s="63"/>
       <c r="AJ29" s="63" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AK29" s="102" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL29" s="63"/>
       <c r="AM29" s="63" t="s">
@@ -7085,16 +7102,16 @@
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="61" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E30" s="61" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F30" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G30" s="61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H30" s="63" t="s">
         <v>47</v>
@@ -7114,7 +7131,7 @@
         <v>48</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P30" s="63">
         <v>6</v>
@@ -7126,7 +7143,7 @@
         <v>50</v>
       </c>
       <c r="S30" s="65">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T30" s="65"/>
       <c r="U30" s="66"/>
@@ -7142,7 +7159,7 @@
         <v>48</v>
       </c>
       <c r="AC30" s="63" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD30" s="63" t="s">
         <v>48</v>
@@ -7157,10 +7174,10 @@
       <c r="AH30" s="63"/>
       <c r="AI30" s="63"/>
       <c r="AJ30" s="63" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AK30" s="102" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL30" s="63"/>
       <c r="AM30" s="63" t="s">
@@ -7172,19 +7189,17 @@
     </row>
     <row r="31" spans="1:42" s="53" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="78" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B31" s="102">
         <v>2024</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="63" t="s">
-        <v>370</v>
-      </c>
-      <c r="E31" s="63" t="s">
         <v>371</v>
       </c>
-      <c r="F31" s="63" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="92" t="s">
         <v>372</v>
       </c>
       <c r="G31" s="63" t="s">
@@ -7258,26 +7273,26 @@
     </row>
     <row r="32" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B32" s="95">
         <v>2024</v>
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E32" s="37" t="s">
         <v>378</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="F32" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="G32" s="37" t="s">
         <v>380</v>
       </c>
-      <c r="G32" s="37" t="s">
-        <v>381</v>
-      </c>
       <c r="H32" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I32" s="37"/>
       <c r="J32" s="37"/>
@@ -7286,7 +7301,7 @@
       <c r="M32" s="37"/>
       <c r="N32" s="37"/>
       <c r="O32" s="37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P32" s="28">
         <v>5</v>
@@ -7298,7 +7313,7 @@
         <v>50</v>
       </c>
       <c r="S32" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" s="28"/>
       <c r="U32" s="39"/>
@@ -7311,26 +7326,26 @@
         <v>51</v>
       </c>
       <c r="AB32" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC32" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD32" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE32" s="37" t="s">
         <v>383</v>
-      </c>
-      <c r="AC32" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD32" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE32" s="37" t="s">
-        <v>384</v>
       </c>
       <c r="AF32" s="37"/>
       <c r="AG32" s="37"/>
       <c r="AH32" s="37"/>
       <c r="AI32" s="37"/>
       <c r="AJ32" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="AK32" s="95" t="s">
         <v>385</v>
-      </c>
-      <c r="AK32" s="95" t="s">
-        <v>386</v>
       </c>
       <c r="AL32" s="37"/>
       <c r="AM32" s="37"/>
@@ -7349,19 +7364,19 @@
         <v>0</v>
       </c>
       <c r="D33" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="F33" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="F33" s="80" t="s">
+      <c r="G33" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="H33" s="23" t="s">
         <v>390</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>391</v>
       </c>
       <c r="I33" s="23" t="s">
         <v>48</v>
@@ -7370,10 +7385,10 @@
         <v>80</v>
       </c>
       <c r="K33" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="L33" s="22" t="s">
         <v>392</v>
-      </c>
-      <c r="L33" s="22" t="s">
-        <v>393</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>62</v>
@@ -7382,7 +7397,7 @@
         <v>50</v>
       </c>
       <c r="O33" s="22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P33" s="22">
         <v>4</v>
@@ -7394,7 +7409,7 @@
         <v>51</v>
       </c>
       <c r="S33" s="27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T33" s="27"/>
       <c r="U33" s="33"/>
@@ -7407,26 +7422,26 @@
         <v>50</v>
       </c>
       <c r="AB33" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC33" s="80" t="s">
         <v>395</v>
       </c>
-      <c r="AC33" s="80" t="s">
+      <c r="AD33" s="105" t="s">
         <v>396</v>
       </c>
-      <c r="AD33" s="105" t="s">
-        <v>397</v>
-      </c>
       <c r="AE33" s="23" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="AF33" s="23"/>
       <c r="AG33" s="23"/>
       <c r="AH33" s="23"/>
       <c r="AI33" s="23"/>
       <c r="AJ33" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="AK33" s="101" t="s">
         <v>398</v>
-      </c>
-      <c r="AK33" s="101" t="s">
-        <v>399</v>
       </c>
       <c r="AL33" s="23"/>
       <c r="AM33" s="31" t="s">
@@ -7445,19 +7460,19 @@
         <v>10</v>
       </c>
       <c r="D34" s="49" t="s">
+        <v>399</v>
+      </c>
+      <c r="E34" s="49" t="s">
         <v>400</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="F34" s="56" t="s">
         <v>401</v>
       </c>
-      <c r="F34" s="56" t="s">
+      <c r="G34" s="49" t="s">
         <v>402</v>
       </c>
-      <c r="G34" s="49" t="s">
-        <v>403</v>
-      </c>
       <c r="H34" s="49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I34" s="49" t="s">
         <v>48</v>
@@ -7466,7 +7481,7 @@
         <v>109</v>
       </c>
       <c r="K34" s="49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L34" s="49" t="s">
         <v>249</v>
@@ -7478,7 +7493,7 @@
         <v>13</v>
       </c>
       <c r="O34" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P34" s="57">
         <v>5</v>
@@ -7490,10 +7505,10 @@
         <v>50</v>
       </c>
       <c r="S34" s="69">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T34" s="69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="U34" s="66"/>
       <c r="V34" s="66"/>
@@ -7505,28 +7520,28 @@
         <v>51</v>
       </c>
       <c r="AB34" s="49" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC34" s="56" t="s">
         <v>406</v>
       </c>
-      <c r="AC34" s="56" t="s">
+      <c r="AD34" s="49" t="s">
         <v>407</v>
       </c>
-      <c r="AD34" s="49" t="s">
+      <c r="AE34" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF34" s="49" t="s">
         <v>408</v>
-      </c>
-      <c r="AE34" s="49" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF34" s="49" t="s">
-        <v>409</v>
       </c>
       <c r="AG34" s="63"/>
       <c r="AH34" s="63"/>
       <c r="AI34" s="63"/>
       <c r="AJ34" s="63" t="s">
+        <v>409</v>
+      </c>
+      <c r="AK34" s="102" t="s">
         <v>410</v>
-      </c>
-      <c r="AK34" s="102" t="s">
-        <v>411</v>
       </c>
       <c r="AL34" s="63"/>
       <c r="AM34" s="57" t="s">
@@ -7547,16 +7562,16 @@
         <v>9</v>
       </c>
       <c r="D35" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="E35" s="49" t="s">
         <v>412</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="F35" s="56" t="s">
         <v>413</v>
       </c>
-      <c r="F35" s="56" t="s">
+      <c r="G35" s="49" t="s">
         <v>414</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>415</v>
       </c>
       <c r="H35" s="49" t="s">
         <v>126</v>
@@ -7568,19 +7583,19 @@
         <v>68</v>
       </c>
       <c r="K35" s="49" t="s">
+        <v>415</v>
+      </c>
+      <c r="L35" s="49" t="s">
         <v>416</v>
-      </c>
-      <c r="L35" s="49" t="s">
-        <v>417</v>
       </c>
       <c r="M35" s="49" t="s">
         <v>62</v>
       </c>
       <c r="N35" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="O35" s="49" t="s">
         <v>418</v>
-      </c>
-      <c r="O35" s="49" t="s">
-        <v>419</v>
       </c>
       <c r="P35" s="46">
         <v>6</v>
@@ -7609,30 +7624,30 @@
         <v>50</v>
       </c>
       <c r="AB35" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC35" s="56" t="s">
         <v>420</v>
       </c>
-      <c r="AC35" s="56" t="s">
+      <c r="AD35" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="AD35" s="49" t="s">
+      <c r="AE35" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="AE35" s="49" t="s">
+      <c r="AF35" s="49" t="s">
         <v>423</v>
-      </c>
-      <c r="AF35" s="49" t="s">
-        <v>424</v>
       </c>
       <c r="AG35" s="63"/>
       <c r="AH35" s="63"/>
       <c r="AI35" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="AJ35" s="63" t="s">
         <v>425</v>
       </c>
-      <c r="AJ35" s="63" t="s">
+      <c r="AK35" s="102" t="s">
         <v>426</v>
-      </c>
-      <c r="AK35" s="102" t="s">
-        <v>427</v>
       </c>
       <c r="AL35" s="63"/>
       <c r="AM35" s="57" t="s">
@@ -7653,13 +7668,13 @@
         <v>8.5</v>
       </c>
       <c r="D36" s="49" t="s">
+        <v>427</v>
+      </c>
+      <c r="E36" s="49" t="s">
         <v>428</v>
       </c>
-      <c r="E36" s="49" t="s">
+      <c r="F36" s="56" t="s">
         <v>429</v>
-      </c>
-      <c r="F36" s="56" t="s">
-        <v>430</v>
       </c>
       <c r="G36" s="47" t="s">
         <v>125</v>
@@ -7674,10 +7689,10 @@
         <v>68</v>
       </c>
       <c r="K36" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="L36" s="46" t="s">
         <v>431</v>
-      </c>
-      <c r="L36" s="46" t="s">
-        <v>432</v>
       </c>
       <c r="M36" s="48" t="s">
         <v>129</v>
@@ -7686,7 +7701,7 @@
         <v>13</v>
       </c>
       <c r="O36" s="46" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P36" s="49">
         <v>4</v>
@@ -7702,7 +7717,7 @@
       </c>
       <c r="T36" s="52"/>
       <c r="U36" s="70" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V36" s="70"/>
       <c r="W36" s="70"/>
@@ -7713,30 +7728,30 @@
         <v>51</v>
       </c>
       <c r="AB36" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC36" s="48" t="s">
         <v>435</v>
       </c>
-      <c r="AC36" s="48" t="s">
+      <c r="AD36" s="48" t="s">
         <v>436</v>
       </c>
-      <c r="AD36" s="48" t="s">
+      <c r="AE36" s="48" t="s">
         <v>437</v>
       </c>
-      <c r="AE36" s="48" t="s">
+      <c r="AF36" s="48" t="s">
         <v>438</v>
-      </c>
-      <c r="AF36" s="48" t="s">
-        <v>439</v>
       </c>
       <c r="AG36" s="48"/>
       <c r="AH36" s="48"/>
       <c r="AI36" s="48" t="s">
+        <v>439</v>
+      </c>
+      <c r="AJ36" s="48" t="s">
         <v>440</v>
       </c>
-      <c r="AJ36" s="48" t="s">
+      <c r="AK36" s="99" t="s">
         <v>441</v>
-      </c>
-      <c r="AK36" s="99" t="s">
-        <v>442</v>
       </c>
       <c r="AL36" s="48"/>
       <c r="AM36" s="57" t="s">
@@ -7757,16 +7772,16 @@
         <v>8</v>
       </c>
       <c r="D37" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="E37" s="55" t="s">
         <v>443</v>
       </c>
-      <c r="E37" s="55" t="s">
+      <c r="F37" s="56" t="s">
         <v>444</v>
       </c>
-      <c r="F37" s="56" t="s">
-        <v>445</v>
-      </c>
       <c r="G37" s="49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H37" s="49" t="s">
         <v>126</v>
@@ -7778,10 +7793,10 @@
         <v>109</v>
       </c>
       <c r="K37" s="49" t="s">
+        <v>445</v>
+      </c>
+      <c r="L37" s="49" t="s">
         <v>446</v>
-      </c>
-      <c r="L37" s="49" t="s">
-        <v>447</v>
       </c>
       <c r="M37" s="49" t="s">
         <v>249</v>
@@ -7790,7 +7805,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="49" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P37" s="49">
         <v>7</v>
@@ -7819,30 +7834,30 @@
         <v>50</v>
       </c>
       <c r="AB37" s="49" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC37" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="AC37" s="56" t="s">
+      <c r="AD37" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE37" s="49" t="s">
         <v>450</v>
       </c>
-      <c r="AD37" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE37" s="49" t="s">
+      <c r="AF37" s="49" t="s">
         <v>451</v>
-      </c>
-      <c r="AF37" s="49" t="s">
-        <v>452</v>
       </c>
       <c r="AG37" s="63"/>
       <c r="AH37" s="63"/>
       <c r="AI37" s="49" t="s">
+        <v>452</v>
+      </c>
+      <c r="AJ37" s="63" t="s">
         <v>453</v>
       </c>
-      <c r="AJ37" s="63" t="s">
+      <c r="AK37" s="102" t="s">
         <v>454</v>
-      </c>
-      <c r="AK37" s="102" t="s">
-        <v>455</v>
       </c>
       <c r="AL37" s="63"/>
       <c r="AM37" s="57" t="s">
@@ -7863,19 +7878,19 @@
         <v>7</v>
       </c>
       <c r="D38" s="49" t="s">
+        <v>455</v>
+      </c>
+      <c r="E38" s="49" t="s">
         <v>456</v>
       </c>
-      <c r="E38" s="49" t="s">
+      <c r="F38" s="56" t="s">
         <v>457</v>
       </c>
-      <c r="F38" s="56" t="s">
+      <c r="G38" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="G38" s="49" t="s">
-        <v>459</v>
-      </c>
       <c r="H38" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I38" s="49" t="s">
         <v>48</v>
@@ -7884,10 +7899,10 @@
         <v>68</v>
       </c>
       <c r="K38" s="49" t="s">
+        <v>459</v>
+      </c>
+      <c r="L38" s="49" t="s">
         <v>460</v>
-      </c>
-      <c r="L38" s="49" t="s">
-        <v>461</v>
       </c>
       <c r="M38" s="49" t="s">
         <v>62</v>
@@ -7896,7 +7911,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P38" s="51">
         <v>6</v>
@@ -7923,30 +7938,30 @@
         <v>51</v>
       </c>
       <c r="AB38" s="49" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC38" s="56" t="s">
         <v>463</v>
       </c>
-      <c r="AC38" s="56" t="s">
+      <c r="AD38" s="49" t="s">
         <v>464</v>
       </c>
-      <c r="AD38" s="49" t="s">
+      <c r="AE38" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF38" s="49" t="s">
         <v>465</v>
-      </c>
-      <c r="AE38" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF38" s="49" t="s">
-        <v>466</v>
       </c>
       <c r="AG38" s="63"/>
       <c r="AH38" s="63"/>
       <c r="AI38" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="AJ38" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="AJ38" s="63" t="s">
+      <c r="AK38" s="102" t="s">
         <v>468</v>
-      </c>
-      <c r="AK38" s="102" t="s">
-        <v>469</v>
       </c>
       <c r="AL38" s="63"/>
       <c r="AM38" s="57" t="s">
@@ -7967,13 +7982,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="E39" s="46" t="s">
         <v>470</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="F39" s="76" t="s">
         <v>471</v>
-      </c>
-      <c r="F39" s="76" t="s">
-        <v>472</v>
       </c>
       <c r="G39" s="47" t="s">
         <v>125</v>
@@ -7988,10 +8003,10 @@
         <v>68</v>
       </c>
       <c r="K39" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="L39" s="46" t="s">
         <v>431</v>
-      </c>
-      <c r="L39" s="46" t="s">
-        <v>432</v>
       </c>
       <c r="M39" s="48" t="s">
         <v>129</v>
@@ -8000,7 +8015,7 @@
         <v>50</v>
       </c>
       <c r="O39" s="46" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P39" s="51">
         <v>5</v>
@@ -8025,30 +8040,30 @@
         <v>51</v>
       </c>
       <c r="AB39" s="48" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC39" s="76" t="s">
         <v>474</v>
       </c>
-      <c r="AC39" s="76" t="s">
+      <c r="AD39" s="48" t="s">
         <v>475</v>
       </c>
-      <c r="AD39" s="48" t="s">
+      <c r="AE39" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF39" s="48" t="s">
         <v>476</v>
-      </c>
-      <c r="AE39" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF39" s="48" t="s">
-        <v>477</v>
       </c>
       <c r="AG39" s="48"/>
       <c r="AH39" s="48"/>
       <c r="AI39" s="48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AJ39" s="48" t="s">
+        <v>477</v>
+      </c>
+      <c r="AK39" s="99" t="s">
         <v>478</v>
-      </c>
-      <c r="AK39" s="99" t="s">
-        <v>479</v>
       </c>
       <c r="AL39" s="48"/>
       <c r="AM39" s="57" t="s">
@@ -8069,13 +8084,13 @@
         <v>6</v>
       </c>
       <c r="D40" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="E40" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="F40" s="80" t="s">
         <v>481</v>
-      </c>
-      <c r="F40" s="80" t="s">
-        <v>482</v>
       </c>
       <c r="G40" s="24" t="s">
         <v>154</v>
@@ -8090,10 +8105,10 @@
         <v>80</v>
       </c>
       <c r="K40" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="L40" s="22" t="s">
         <v>483</v>
-      </c>
-      <c r="L40" s="22" t="s">
-        <v>484</v>
       </c>
       <c r="M40" s="23" t="s">
         <v>129</v>
@@ -8102,7 +8117,7 @@
         <v>50</v>
       </c>
       <c r="O40" s="22" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P40" s="25">
         <v>6</v>
@@ -8114,7 +8129,7 @@
         <v>51</v>
       </c>
       <c r="S40" s="27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T40" s="27"/>
       <c r="U40" s="33"/>
@@ -8127,26 +8142,26 @@
         <v>50</v>
       </c>
       <c r="AB40" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC40" s="80" t="s">
         <v>486</v>
-      </c>
-      <c r="AC40" s="80" t="s">
-        <v>487</v>
       </c>
       <c r="AD40" s="23"/>
       <c r="AE40" s="23" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AF40" s="23"/>
       <c r="AG40" s="23"/>
       <c r="AH40" s="23"/>
       <c r="AI40" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="AJ40" s="23" t="s">
         <v>489</v>
       </c>
-      <c r="AJ40" s="23" t="s">
+      <c r="AK40" s="101" t="s">
         <v>490</v>
-      </c>
-      <c r="AK40" s="101" t="s">
-        <v>491</v>
       </c>
       <c r="AL40" s="23"/>
       <c r="AM40" s="31" t="s">
@@ -8167,31 +8182,31 @@
         <v>0</v>
       </c>
       <c r="D41" s="46" t="s">
+        <v>491</v>
+      </c>
+      <c r="E41" s="46" t="s">
         <v>492</v>
       </c>
-      <c r="E41" s="46" t="s">
+      <c r="F41" s="76" t="s">
         <v>493</v>
       </c>
-      <c r="F41" s="76" t="s">
+      <c r="G41" s="47" t="s">
         <v>494</v>
       </c>
-      <c r="G41" s="47" t="s">
+      <c r="H41" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="H41" s="48" t="s">
+      <c r="I41" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="49" t="s">
         <v>496</v>
       </c>
-      <c r="I41" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="J41" s="49" t="s">
+      <c r="K41" s="46" t="s">
         <v>497</v>
       </c>
-      <c r="K41" s="46" t="s">
+      <c r="L41" s="46" t="s">
         <v>498</v>
-      </c>
-      <c r="L41" s="46" t="s">
-        <v>499</v>
       </c>
       <c r="M41" s="48" t="s">
         <v>62</v>
@@ -8200,7 +8215,7 @@
         <v>50</v>
       </c>
       <c r="O41" s="46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P41" s="51">
         <v>7</v>
@@ -8228,27 +8243,27 @@
         <v>48</v>
       </c>
       <c r="AC41" s="48" t="s">
+        <v>500</v>
+      </c>
+      <c r="AD41" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="AD41" s="48" t="s">
+      <c r="AE41" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF41" s="48" t="s">
         <v>502</v>
-      </c>
-      <c r="AE41" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF41" s="48" t="s">
-        <v>503</v>
       </c>
       <c r="AG41" s="48"/>
       <c r="AH41" s="48"/>
       <c r="AI41" s="48" t="s">
+        <v>503</v>
+      </c>
+      <c r="AJ41" s="48" t="s">
         <v>504</v>
       </c>
-      <c r="AJ41" s="48" t="s">
+      <c r="AK41" s="99" t="s">
         <v>505</v>
-      </c>
-      <c r="AK41" s="99" t="s">
-        <v>506</v>
       </c>
       <c r="AL41" s="48"/>
       <c r="AM41" s="57" t="s">
@@ -8269,16 +8284,16 @@
         <v>0</v>
       </c>
       <c r="D42" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="E42" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="F42" s="80" t="s">
         <v>508</v>
       </c>
-      <c r="F42" s="80" t="s">
+      <c r="G42" s="24" t="s">
         <v>509</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>510</v>
       </c>
       <c r="H42" s="23" t="s">
         <v>126</v>
@@ -8290,7 +8305,7 @@
         <v>48</v>
       </c>
       <c r="K42" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L42" s="24"/>
       <c r="M42" s="23" t="s">
@@ -8300,7 +8315,7 @@
         <v>50</v>
       </c>
       <c r="O42" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P42" s="22">
         <v>6</v>
@@ -8326,23 +8341,23 @@
       </c>
       <c r="AB42" s="23"/>
       <c r="AC42" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AD42" s="23" t="s">
         <v>48</v>
       </c>
       <c r="AE42" s="23" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF42" s="23"/>
       <c r="AG42" s="23"/>
       <c r="AH42" s="23"/>
       <c r="AI42" s="23"/>
       <c r="AJ42" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="AK42" s="101" t="s">
         <v>514</v>
-      </c>
-      <c r="AK42" s="101" t="s">
-        <v>515</v>
       </c>
       <c r="AL42" s="23"/>
       <c r="AM42" s="23" t="s">
@@ -8363,19 +8378,19 @@
         <v>0</v>
       </c>
       <c r="D43" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="E43" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="F43" s="23" t="s">
         <v>517</v>
       </c>
-      <c r="F43" s="23" t="s">
+      <c r="G43" s="24" t="s">
         <v>518</v>
       </c>
-      <c r="G43" s="24" t="s">
-        <v>519</v>
-      </c>
       <c r="H43" s="23" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I43" s="23" t="s">
         <v>48</v>
@@ -8384,10 +8399,10 @@
         <v>109</v>
       </c>
       <c r="K43" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="L43" s="22" t="s">
         <v>520</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>521</v>
       </c>
       <c r="M43" s="23" t="s">
         <v>62</v>
@@ -8396,7 +8411,7 @@
         <v>50</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P43" s="22">
         <v>4</v>
@@ -8408,7 +8423,7 @@
         <v>51</v>
       </c>
       <c r="S43" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T43" s="27"/>
       <c r="U43" s="33"/>
@@ -8421,33 +8436,34 @@
         <v>50</v>
       </c>
       <c r="AB43" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="AC43" s="80" t="s">
         <v>522</v>
       </c>
-      <c r="AC43" s="80" t="s">
+      <c r="AD43" s="23" t="s">
         <v>523</v>
       </c>
-      <c r="AD43" s="23" t="s">
-        <v>524</v>
-      </c>
       <c r="AE43" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF43" s="23"/>
       <c r="AG43" s="23"/>
       <c r="AH43" s="23"/>
       <c r="AI43" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="AJ43" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="AJ43" s="23" t="s">
+      <c r="AK43" s="101" t="s">
         <v>526</v>
-      </c>
-      <c r="AK43" s="101" t="s">
-        <v>527</v>
       </c>
       <c r="AL43" s="23"/>
       <c r="AM43" s="23" t="s">
         <v>55</v>
       </c>
+      <c r="AP43"/>
     </row>
     <row r="44" spans="1:42" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="37" t="s">
@@ -8460,16 +8476,16 @@
         <v>0</v>
       </c>
       <c r="D44" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="E44" s="22" t="s">
         <v>528</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="F44" s="80" t="s">
         <v>529</v>
       </c>
-      <c r="F44" s="80" t="s">
+      <c r="G44" s="24" t="s">
         <v>530</v>
-      </c>
-      <c r="G44" s="24" t="s">
-        <v>531</v>
       </c>
       <c r="H44" s="23" t="s">
         <v>108</v>
@@ -8481,10 +8497,10 @@
         <v>68</v>
       </c>
       <c r="K44" s="22" t="s">
+        <v>531</v>
+      </c>
+      <c r="L44" s="22" t="s">
         <v>532</v>
-      </c>
-      <c r="L44" s="22" t="s">
-        <v>533</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>62</v>
@@ -8493,7 +8509,7 @@
         <v>50</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P44" s="22">
         <v>7</v>
@@ -8521,23 +8537,23 @@
         <v>48</v>
       </c>
       <c r="AC44" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="AD44" s="23" t="s">
         <v>535</v>
       </c>
-      <c r="AD44" s="23" t="s">
-        <v>536</v>
-      </c>
       <c r="AE44" s="23" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF44" s="23"/>
       <c r="AG44" s="23"/>
       <c r="AH44" s="23"/>
       <c r="AI44" s="23"/>
       <c r="AJ44" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="AK44" s="101" t="s">
         <v>537</v>
-      </c>
-      <c r="AK44" s="101" t="s">
-        <v>538</v>
       </c>
       <c r="AL44" s="23"/>
       <c r="AM44" s="23" t="s">
@@ -8555,19 +8571,19 @@
         <v>0</v>
       </c>
       <c r="D45" s="22" t="s">
+        <v>538</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="F45" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="F45" s="23" t="s">
-        <v>541</v>
-      </c>
       <c r="G45" s="24" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>48</v>
@@ -8576,10 +8592,10 @@
         <v>109</v>
       </c>
       <c r="K45" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="L45" s="22" t="s">
         <v>520</v>
-      </c>
-      <c r="L45" s="22" t="s">
-        <v>521</v>
       </c>
       <c r="M45" s="23" t="s">
         <v>62</v>
@@ -8588,7 +8604,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P45" s="35">
         <v>6</v>
@@ -8600,7 +8616,7 @@
         <v>51</v>
       </c>
       <c r="S45" s="27">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="T45" s="27"/>
       <c r="U45" s="33"/>
@@ -8613,26 +8629,26 @@
         <v>50</v>
       </c>
       <c r="AB45" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="AC45" s="80" t="s">
         <v>543</v>
       </c>
-      <c r="AC45" s="80" t="s">
+      <c r="AD45" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="AD45" s="23" t="s">
-        <v>545</v>
-      </c>
       <c r="AE45" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF45" s="23"/>
       <c r="AG45" s="23"/>
       <c r="AH45" s="23"/>
       <c r="AI45" s="23"/>
       <c r="AJ45" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK45" s="101" t="s">
         <v>546</v>
-      </c>
-      <c r="AK45" s="101" t="s">
-        <v>547</v>
       </c>
       <c r="AL45" s="23"/>
       <c r="AM45" s="23" t="s">
@@ -8648,34 +8664,34 @@
         <v>2025</v>
       </c>
       <c r="D46" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="E46" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="E46" s="35" t="s">
+      <c r="F46" s="36" t="s">
         <v>549</v>
       </c>
-      <c r="F46" s="36" t="s">
+      <c r="G46" s="35" t="s">
         <v>550</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>551</v>
       </c>
       <c r="H46" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I46" s="38" t="s">
+        <v>551</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="M46" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="N46" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="O46" s="35" t="s">
         <v>552</v>
-      </c>
-      <c r="J46" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="M46" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N46" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="O46" s="35" t="s">
-        <v>553</v>
       </c>
       <c r="P46" s="87">
         <v>5</v>
@@ -8693,22 +8709,22 @@
         <v>50</v>
       </c>
       <c r="AB46" s="88" t="s">
+        <v>553</v>
+      </c>
+      <c r="AC46" s="80" t="s">
         <v>554</v>
       </c>
-      <c r="AC46" s="80" t="s">
+      <c r="AD46" s="37" t="s">
         <v>555</v>
       </c>
-      <c r="AD46" s="37" t="s">
+      <c r="AE46" s="37" t="s">
         <v>556</v>
       </c>
-      <c r="AE46" s="37" t="s">
+      <c r="AJ46" s="37" t="s">
         <v>557</v>
       </c>
-      <c r="AJ46" s="37" t="s">
+      <c r="AK46" s="95" t="s">
         <v>558</v>
-      </c>
-      <c r="AK46" s="95" t="s">
-        <v>559</v>
       </c>
       <c r="AM46" s="37" t="s">
         <v>55</v>
@@ -8724,22 +8740,22 @@
         <v>2025</v>
       </c>
       <c r="D47" s="35" t="s">
+        <v>559</v>
+      </c>
+      <c r="E47" s="35" t="s">
         <v>560</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="F47" s="36" t="s">
         <v>561</v>
       </c>
-      <c r="F47" s="36" t="s">
-        <v>562</v>
-      </c>
       <c r="G47" s="35" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H47" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I47" s="38" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J47" s="37" t="s">
         <v>48</v>
@@ -8751,7 +8767,7 @@
         <v>48</v>
       </c>
       <c r="O47" s="35" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="P47" s="87">
         <v>5</v>
@@ -8769,19 +8785,19 @@
         <v>50</v>
       </c>
       <c r="AB47" s="88" t="s">
+        <v>563</v>
+      </c>
+      <c r="AD47" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE47" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ47" s="37" t="s">
         <v>564</v>
       </c>
-      <c r="AD47" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE47" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ47" s="37" t="s">
+      <c r="AK47" s="95" t="s">
         <v>565</v>
-      </c>
-      <c r="AK47" s="95" t="s">
-        <v>566</v>
       </c>
       <c r="AM47" s="37" t="s">
         <v>55</v>
@@ -8796,22 +8812,22 @@
         <v>2025</v>
       </c>
       <c r="D48" s="61" t="s">
+        <v>566</v>
+      </c>
+      <c r="E48" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" s="62" t="s">
         <v>567</v>
       </c>
-      <c r="E48" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="62" t="s">
+      <c r="G48" s="61" t="s">
         <v>568</v>
       </c>
-      <c r="G48" s="61" t="s">
+      <c r="H48" s="63" t="s">
         <v>569</v>
       </c>
-      <c r="H48" s="63" t="s">
+      <c r="I48" s="78" t="s">
         <v>570</v>
-      </c>
-      <c r="I48" s="78" t="s">
-        <v>571</v>
       </c>
       <c r="J48" s="63" t="s">
         <v>48</v>
@@ -8825,7 +8841,7 @@
         <v>48</v>
       </c>
       <c r="O48" s="61" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P48" s="63">
         <v>4</v>
@@ -8866,10 +8882,10 @@
       <c r="AH48" s="63"/>
       <c r="AI48" s="63"/>
       <c r="AJ48" s="63" t="s">
+        <v>572</v>
+      </c>
+      <c r="AK48" s="102" t="s">
         <v>573</v>
-      </c>
-      <c r="AK48" s="102" t="s">
-        <v>574</v>
       </c>
       <c r="AL48" s="63"/>
       <c r="AM48" s="63" t="s">
@@ -8888,25 +8904,25 @@
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="35" t="s">
+        <v>574</v>
+      </c>
+      <c r="E49" s="35" t="s">
         <v>575</v>
       </c>
-      <c r="E49" s="35" t="s">
+      <c r="F49" s="40" t="s">
         <v>576</v>
       </c>
-      <c r="F49" s="40" t="s">
+      <c r="G49" s="35" t="s">
         <v>577</v>
       </c>
-      <c r="G49" s="35" t="s">
+      <c r="H49" s="37" t="s">
         <v>578</v>
       </c>
-      <c r="H49" s="37" t="s">
+      <c r="I49" s="38" t="s">
+        <v>551</v>
+      </c>
+      <c r="J49" s="37" t="s">
         <v>579</v>
-      </c>
-      <c r="I49" s="38" t="s">
-        <v>552</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>580</v>
       </c>
       <c r="K49" s="37"/>
       <c r="L49" s="37"/>
@@ -8917,7 +8933,7 @@
         <v>48</v>
       </c>
       <c r="O49" s="35" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P49" s="37">
         <v>25</v>
@@ -8929,7 +8945,7 @@
         <v>51</v>
       </c>
       <c r="S49" s="28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" s="28"/>
       <c r="U49" s="39"/>
@@ -8942,13 +8958,13 @@
         <v>51</v>
       </c>
       <c r="AB49" s="37" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC49" s="80" t="s">
         <v>582</v>
       </c>
-      <c r="AC49" s="80" t="s">
+      <c r="AD49" s="37" t="s">
         <v>583</v>
-      </c>
-      <c r="AD49" s="37" t="s">
-        <v>584</v>
       </c>
       <c r="AE49" s="37" t="s">
         <v>48</v>
@@ -8958,10 +8974,10 @@
       <c r="AH49" s="37"/>
       <c r="AI49" s="37"/>
       <c r="AJ49" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="AK49" s="95" t="s">
         <v>585</v>
-      </c>
-      <c r="AK49" s="95" t="s">
-        <v>586</v>
       </c>
       <c r="AL49" s="37"/>
       <c r="AM49" s="37" t="s">
@@ -8979,22 +8995,22 @@
         <v>2025</v>
       </c>
       <c r="D50" s="61" t="s">
+        <v>586</v>
+      </c>
+      <c r="E50" s="61" t="s">
         <v>587</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="F50" s="71" t="s">
         <v>588</v>
       </c>
-      <c r="F50" s="71" t="s">
+      <c r="G50" s="61" t="s">
         <v>589</v>
       </c>
-      <c r="G50" s="61" t="s">
-        <v>590</v>
-      </c>
       <c r="H50" s="63" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I50" s="64" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J50" s="63" t="s">
         <v>48</v>
@@ -9008,7 +9024,7 @@
         <v>48</v>
       </c>
       <c r="O50" s="61" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P50" s="63">
         <v>6</v>
@@ -9033,16 +9049,16 @@
         <v>51</v>
       </c>
       <c r="AB50" s="63" t="s">
+        <v>591</v>
+      </c>
+      <c r="AC50" s="76" t="s">
         <v>592</v>
       </c>
-      <c r="AC50" s="76" t="s">
-        <v>593</v>
-      </c>
       <c r="AD50" s="63" t="s">
         <v>48</v>
       </c>
       <c r="AE50" s="63" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF50" s="63" t="s">
         <v>48</v>
@@ -9051,10 +9067,10 @@
       <c r="AH50" s="63"/>
       <c r="AI50" s="63"/>
       <c r="AJ50" s="63" t="s">
+        <v>593</v>
+      </c>
+      <c r="AK50" s="102" t="s">
         <v>594</v>
-      </c>
-      <c r="AK50" s="102" t="s">
-        <v>595</v>
       </c>
       <c r="AL50" s="63"/>
       <c r="AM50" s="48" t="s">
@@ -9073,22 +9089,22 @@
       </c>
       <c r="C51" s="28"/>
       <c r="D51" s="61" t="s">
+        <v>595</v>
+      </c>
+      <c r="E51" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="F51" s="71" t="s">
         <v>597</v>
       </c>
-      <c r="F51" s="71" t="s">
+      <c r="G51" s="61" t="s">
         <v>598</v>
-      </c>
-      <c r="G51" s="61" t="s">
-        <v>599</v>
       </c>
       <c r="H51" s="63" t="s">
         <v>126</v>
       </c>
       <c r="I51" s="64" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J51" s="63" t="s">
         <v>48</v>
@@ -9102,7 +9118,7 @@
         <v>48</v>
       </c>
       <c r="O51" s="61" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="P51" s="63">
         <v>6</v>
@@ -9114,7 +9130,7 @@
         <v>50</v>
       </c>
       <c r="S51" s="65">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T51" s="65"/>
       <c r="U51" s="66"/>
@@ -9127,13 +9143,13 @@
         <v>50</v>
       </c>
       <c r="AB51" s="63" t="s">
+        <v>601</v>
+      </c>
+      <c r="AC51" s="76" t="s">
         <v>602</v>
       </c>
-      <c r="AC51" s="76" t="s">
+      <c r="AD51" s="63" t="s">
         <v>603</v>
-      </c>
-      <c r="AD51" s="63" t="s">
-        <v>604</v>
       </c>
       <c r="AE51" s="63" t="s">
         <v>48</v>
@@ -9145,10 +9161,10 @@
       <c r="AH51" s="63"/>
       <c r="AI51" s="63"/>
       <c r="AJ51" s="63" t="s">
+        <v>604</v>
+      </c>
+      <c r="AK51" s="102" t="s">
         <v>605</v>
-      </c>
-      <c r="AK51" s="102" t="s">
-        <v>606</v>
       </c>
       <c r="AL51" s="63"/>
       <c r="AM51" s="63" t="s">
@@ -9167,25 +9183,25 @@
       </c>
       <c r="C52" s="28"/>
       <c r="D52" s="35" t="s">
+        <v>606</v>
+      </c>
+      <c r="E52" s="35" t="s">
         <v>607</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="F52" s="88" t="s">
         <v>608</v>
       </c>
-      <c r="F52" s="88" t="s">
+      <c r="G52" s="35" t="s">
         <v>609</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>610</v>
       </c>
       <c r="H52" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I52" s="38" t="s">
+        <v>610</v>
+      </c>
+      <c r="J52" s="37" t="s">
         <v>611</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>612</v>
       </c>
       <c r="K52" s="37"/>
       <c r="L52" s="37"/>
@@ -9196,7 +9212,7 @@
         <v>48</v>
       </c>
       <c r="O52" s="35" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P52" s="37">
         <v>6</v>
@@ -9237,10 +9253,10 @@
       <c r="AH52" s="37"/>
       <c r="AI52" s="37"/>
       <c r="AJ52" s="37" t="s">
+        <v>613</v>
+      </c>
+      <c r="AK52" s="95" t="s">
         <v>614</v>
-      </c>
-      <c r="AK52" s="95" t="s">
-        <v>615</v>
       </c>
       <c r="AL52" s="37"/>
       <c r="AM52" s="23" t="s">
@@ -9258,22 +9274,22 @@
         <v>2025</v>
       </c>
       <c r="D53" s="61" t="s">
+        <v>615</v>
+      </c>
+      <c r="E53" s="61" t="s">
         <v>616</v>
       </c>
-      <c r="E53" s="61" t="s">
+      <c r="F53" s="62" t="s">
         <v>617</v>
       </c>
-      <c r="F53" s="62" t="s">
+      <c r="G53" s="61" t="s">
         <v>618</v>
       </c>
-      <c r="G53" s="61" t="s">
+      <c r="H53" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="I53" s="64" t="s">
         <v>619</v>
-      </c>
-      <c r="H53" s="63" t="s">
-        <v>340</v>
-      </c>
-      <c r="I53" s="64" t="s">
-        <v>620</v>
       </c>
       <c r="J53" s="63" t="s">
         <v>48</v>
@@ -9287,7 +9303,7 @@
         <v>48</v>
       </c>
       <c r="O53" s="61" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P53" s="63">
         <v>6</v>
@@ -9330,10 +9346,10 @@
       <c r="AH53" s="63"/>
       <c r="AI53" s="63"/>
       <c r="AJ53" s="63" t="s">
+        <v>621</v>
+      </c>
+      <c r="AK53" s="102" t="s">
         <v>622</v>
-      </c>
-      <c r="AK53" s="102" t="s">
-        <v>623</v>
       </c>
       <c r="AL53" s="63"/>
       <c r="AM53" s="63" t="s">
@@ -9345,20 +9361,20 @@
     </row>
     <row r="54" spans="1:42" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B54" s="82">
         <v>2025</v>
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="61" t="s">
+        <v>623</v>
+      </c>
+      <c r="E54" s="61" t="s">
         <v>624</v>
       </c>
-      <c r="E54" s="61" t="s">
+      <c r="F54" s="62" t="s">
         <v>625</v>
-      </c>
-      <c r="F54" s="62" t="s">
-        <v>626</v>
       </c>
       <c r="G54" s="64" t="s">
         <v>108</v>
@@ -9381,7 +9397,7 @@
         <v>48</v>
       </c>
       <c r="O54" s="63" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P54" s="63">
         <v>4</v>
@@ -9424,10 +9440,10 @@
       <c r="AH54" s="63"/>
       <c r="AI54" s="63"/>
       <c r="AJ54" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="AK54" s="102" t="s">
         <v>628</v>
-      </c>
-      <c r="AK54" s="102" t="s">
-        <v>629</v>
       </c>
       <c r="AL54" s="63"/>
       <c r="AM54" s="63" t="s">
@@ -9446,16 +9462,14 @@
       </c>
       <c r="C55" s="28"/>
       <c r="D55" s="61" t="s">
+        <v>629</v>
+      </c>
+      <c r="E55" s="61"/>
+      <c r="F55" s="62" t="s">
         <v>630</v>
       </c>
-      <c r="E55" s="61" t="s">
-        <v>631</v>
-      </c>
-      <c r="F55" s="62" t="s">
-        <v>632</v>
-      </c>
       <c r="G55" s="61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H55" s="63" t="s">
         <v>183</v>
@@ -9475,7 +9489,7 @@
         <v>48</v>
       </c>
       <c r="O55" s="61" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="P55" s="63">
         <v>6</v>
@@ -9503,7 +9517,7 @@
         <v>48</v>
       </c>
       <c r="AC55" s="63" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AD55" s="63" t="s">
         <v>48</v>
@@ -9518,10 +9532,10 @@
       <c r="AH55" s="63"/>
       <c r="AI55" s="63"/>
       <c r="AJ55" s="63" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AK55" s="102" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AL55" s="63"/>
       <c r="AM55" s="63" t="s">
@@ -9540,16 +9554,14 @@
       </c>
       <c r="C56" s="28"/>
       <c r="D56" s="61" t="s">
-        <v>637</v>
-      </c>
-      <c r="E56" s="61" t="s">
-        <v>638</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="E56" s="61"/>
       <c r="F56" s="62" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G56" s="61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H56" s="63" t="s">
         <v>183</v>
@@ -9569,7 +9581,7 @@
         <v>48</v>
       </c>
       <c r="O56" s="61" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="P56" s="63">
         <v>3</v>
@@ -9597,7 +9609,7 @@
         <v>48</v>
       </c>
       <c r="AC56" s="63" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AD56" s="63" t="s">
         <v>48</v>
@@ -9612,10 +9624,10 @@
       <c r="AH56" s="63"/>
       <c r="AI56" s="63"/>
       <c r="AJ56" s="63" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="AK56" s="102" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AL56" s="63"/>
       <c r="AM56" s="63" t="s">
@@ -9627,26 +9639,26 @@
     </row>
     <row r="57" spans="1:42" s="54" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B57" s="37">
         <v>2025</v>
       </c>
       <c r="C57" s="28"/>
       <c r="D57" s="37" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I57" s="37"/>
       <c r="J57" s="37"/>
@@ -9655,7 +9667,7 @@
       <c r="M57" s="37"/>
       <c r="N57" s="37"/>
       <c r="O57" s="37" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="P57" s="28">
         <v>4</v>
@@ -9680,11 +9692,11 @@
         <v>51</v>
       </c>
       <c r="AB57" s="37" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="AC57" s="37"/>
       <c r="AD57" s="37" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="AE57" s="37" t="s">
         <v>48</v>
@@ -9694,14 +9706,14 @@
       <c r="AH57" s="37"/>
       <c r="AI57" s="37"/>
       <c r="AJ57" s="37" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AK57" s="95" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="AL57" s="37"/>
       <c r="AM57" s="37" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AN57" s="37"/>
       <c r="AO57" s="37"/>
@@ -9718,19 +9730,19 @@
         <v>10</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F58" s="80" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I58" s="37" t="s">
         <v>48</v>
@@ -9739,7 +9751,7 @@
         <v>109</v>
       </c>
       <c r="K58" s="49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L58" s="49" t="s">
         <v>249</v>
@@ -9751,7 +9763,7 @@
         <v>50</v>
       </c>
       <c r="O58" s="37" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="P58" s="28">
         <v>5</v>
@@ -9763,37 +9775,37 @@
         <v>51</v>
       </c>
       <c r="S58" s="28">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA58" s="37" t="s">
         <v>51</v>
       </c>
       <c r="AB58" s="37" t="s">
+        <v>653</v>
+      </c>
+      <c r="AC58" s="37" t="s">
+        <v>654</v>
+      </c>
+      <c r="AD58" s="104" t="s">
+        <v>655</v>
+      </c>
+      <c r="AE58" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="AF58" s="37" t="s">
         <v>656</v>
       </c>
-      <c r="AC58" s="37" t="s">
+      <c r="AJ58" s="37" t="s">
         <v>657</v>
       </c>
-      <c r="AD58" s="104" t="s">
+      <c r="AK58" s="95" t="s">
         <v>658</v>
-      </c>
-      <c r="AE58" s="37" t="s">
-        <v>488</v>
-      </c>
-      <c r="AF58" s="37" t="s">
-        <v>659</v>
-      </c>
-      <c r="AJ58" s="37" t="s">
-        <v>660</v>
-      </c>
-      <c r="AK58" s="95" t="s">
-        <v>661</v>
       </c>
       <c r="AM58" s="37" t="s">
         <v>55</v>
       </c>
       <c r="AO58" s="37" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AP58"/>
     </row>
@@ -9808,19 +9820,19 @@
         <v>10</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F59" s="92" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I59" s="37" t="s">
         <v>48</v>
@@ -9829,7 +9841,7 @@
         <v>109</v>
       </c>
       <c r="K59" s="49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L59" s="49" t="s">
         <v>249</v>
@@ -9841,7 +9853,7 @@
         <v>51</v>
       </c>
       <c r="O59" s="37" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="P59" s="28">
         <v>6</v>
@@ -9859,33 +9871,32 @@
         <v>51</v>
       </c>
       <c r="AB59" s="37" t="s">
+        <v>664</v>
+      </c>
+      <c r="AC59" s="92" t="s">
+        <v>665</v>
+      </c>
+      <c r="AD59" s="37" t="s">
+        <v>666</v>
+      </c>
+      <c r="AE59" s="37" t="s">
         <v>667</v>
       </c>
-      <c r="AC59" s="92" t="s">
+      <c r="AF59" s="37" t="s">
         <v>668</v>
       </c>
-      <c r="AD59" s="37" t="s">
+      <c r="AJ59" s="37" t="s">
         <v>669</v>
       </c>
-      <c r="AE59" s="37" t="s">
+      <c r="AK59" s="95" t="s">
         <v>670</v>
       </c>
-      <c r="AF59" s="37" t="s">
-        <v>848</v>
-      </c>
-      <c r="AJ59" s="37" t="s">
+      <c r="AM59" s="37" t="s">
         <v>671</v>
       </c>
-      <c r="AK59" s="95" t="s">
+      <c r="AO59" s="37" t="s">
         <v>672</v>
       </c>
-      <c r="AM59" s="37" t="s">
-        <v>673</v>
-      </c>
-      <c r="AO59" s="37" t="s">
-        <v>674</v>
-      </c>
-      <c r="AP59"/>
     </row>
     <row r="60" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="78" t="s">
@@ -9898,19 +9909,19 @@
         <v>0</v>
       </c>
       <c r="D60" s="63" t="s">
+        <v>673</v>
+      </c>
+      <c r="E60" s="63" t="s">
+        <v>674</v>
+      </c>
+      <c r="F60" s="108" t="s">
         <v>675</v>
       </c>
-      <c r="E60" s="63" t="s">
-        <v>676</v>
-      </c>
-      <c r="F60" s="108" t="s">
-        <v>677</v>
-      </c>
       <c r="G60" s="47" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H60" s="48" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I60" s="48" t="s">
         <v>48</v>
@@ -9919,10 +9930,10 @@
         <v>109</v>
       </c>
       <c r="K60" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="L60" s="46" t="s">
         <v>520</v>
-      </c>
-      <c r="L60" s="46" t="s">
-        <v>521</v>
       </c>
       <c r="M60" s="48" t="s">
         <v>62</v>
@@ -9931,7 +9942,7 @@
         <v>50</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="P60" s="65">
         <v>10</v>
@@ -9943,7 +9954,7 @@
         <v>51</v>
       </c>
       <c r="S60" s="65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T60" s="65"/>
       <c r="U60" s="66"/>
@@ -9956,30 +9967,30 @@
         <v>51</v>
       </c>
       <c r="AB60" s="63" t="s">
+        <v>677</v>
+      </c>
+      <c r="AC60" s="108" t="s">
+        <v>678</v>
+      </c>
+      <c r="AD60" s="63" t="s">
         <v>679</v>
       </c>
-      <c r="AC60" s="108" t="s">
+      <c r="AE60" s="63" t="s">
         <v>680</v>
       </c>
-      <c r="AD60" s="63" t="s">
+      <c r="AF60" s="63" t="s">
         <v>681</v>
       </c>
-      <c r="AE60" s="63" t="s">
+      <c r="AG60" s="63" t="s">
         <v>682</v>
-      </c>
-      <c r="AF60" s="63" t="s">
-        <v>683</v>
-      </c>
-      <c r="AG60" s="63" t="s">
-        <v>684</v>
       </c>
       <c r="AH60" s="63"/>
       <c r="AI60" s="63"/>
       <c r="AJ60" s="63" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AK60" s="102" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AL60" s="63"/>
       <c r="AM60" s="63" t="s">
@@ -10000,13 +10011,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="22" t="s">
+        <v>685</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>686</v>
+      </c>
+      <c r="F61" s="80" t="s">
         <v>687</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>688</v>
-      </c>
-      <c r="F61" s="80" t="s">
-        <v>689</v>
       </c>
       <c r="G61" s="24" t="s">
         <v>154</v>
@@ -10021,10 +10032,10 @@
         <v>80</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M61" s="23" t="s">
         <v>129</v>
@@ -10033,7 +10044,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="P61" s="22">
         <v>6</v>
@@ -10058,35 +10069,34 @@
         <v>50</v>
       </c>
       <c r="AB61" s="23" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AC61" s="23"/>
       <c r="AD61" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="AE61" s="23" t="s">
+        <v>692</v>
+      </c>
+      <c r="AF61" s="23" t="s">
         <v>693</v>
-      </c>
-      <c r="AE61" s="23" t="s">
-        <v>694</v>
-      </c>
-      <c r="AF61" s="23" t="s">
-        <v>695</v>
       </c>
       <c r="AG61" s="23"/>
       <c r="AH61" s="23"/>
       <c r="AI61" s="23" t="s">
+        <v>694</v>
+      </c>
+      <c r="AJ61" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="AK61" s="101" t="s">
         <v>696</v>
-      </c>
-      <c r="AJ61" s="23" t="s">
-        <v>697</v>
-      </c>
-      <c r="AK61" s="101" t="s">
-        <v>698</v>
       </c>
       <c r="AL61" s="23"/>
       <c r="AM61" s="23" t="s">
         <v>55</v>
       </c>
       <c r="AO61" s="2"/>
-      <c r="AP61"/>
     </row>
     <row r="62" spans="1:42" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="63" t="s">
@@ -10099,16 +10109,16 @@
         <v>7</v>
       </c>
       <c r="D62" s="46" t="s">
+        <v>697</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>698</v>
+      </c>
+      <c r="F62" s="108" t="s">
         <v>699</v>
       </c>
-      <c r="E62" s="46" t="s">
+      <c r="G62" s="47" t="s">
         <v>700</v>
-      </c>
-      <c r="F62" s="108" t="s">
-        <v>701</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>702</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>126</v>
@@ -10120,10 +10130,10 @@
         <v>68</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="L62" s="46" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="M62" s="48" t="s">
         <v>129</v>
@@ -10132,7 +10142,7 @@
         <v>51</v>
       </c>
       <c r="O62" s="46" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="P62" s="57">
         <v>5</v>
@@ -10144,7 +10154,7 @@
         <v>51</v>
       </c>
       <c r="S62" s="52">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T62" s="52"/>
       <c r="U62" s="70"/>
@@ -10157,28 +10167,28 @@
         <v>51</v>
       </c>
       <c r="AB62" s="48" t="s">
+        <v>704</v>
+      </c>
+      <c r="AC62" s="90" t="s">
+        <v>705</v>
+      </c>
+      <c r="AD62" s="48" t="s">
         <v>706</v>
       </c>
-      <c r="AC62" s="90" t="s">
+      <c r="AE62" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF62" s="48" t="s">
         <v>707</v>
-      </c>
-      <c r="AD62" s="48" t="s">
-        <v>708</v>
-      </c>
-      <c r="AE62" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF62" s="48" t="s">
-        <v>709</v>
       </c>
       <c r="AG62" s="48"/>
       <c r="AH62" s="48"/>
       <c r="AI62" s="48"/>
       <c r="AJ62" s="48" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AK62" s="99" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AL62" s="48"/>
       <c r="AM62" s="48" t="s">
@@ -10199,19 +10209,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
+        <v>710</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>711</v>
+      </c>
+      <c r="F63" s="80" t="s">
         <v>712</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="G63" s="24" t="s">
         <v>713</v>
       </c>
-      <c r="F63" s="80" t="s">
+      <c r="H63" s="23" t="s">
         <v>714</v>
-      </c>
-      <c r="G63" s="24" t="s">
-        <v>715</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>716</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>48</v>
@@ -10220,10 +10230,10 @@
         <v>109</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L63" s="22" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>62</v>
@@ -10232,7 +10242,7 @@
         <v>50</v>
       </c>
       <c r="O63" s="22" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="P63" s="87">
         <v>10</v>
@@ -10244,7 +10254,7 @@
         <v>51</v>
       </c>
       <c r="S63" s="27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T63" s="27"/>
       <c r="U63" s="33"/>
@@ -10257,26 +10267,26 @@
         <v>51</v>
       </c>
       <c r="AB63" s="91" t="s">
+        <v>718</v>
+      </c>
+      <c r="AC63" s="80" t="s">
+        <v>719</v>
+      </c>
+      <c r="AD63" s="23" t="s">
         <v>720</v>
       </c>
-      <c r="AC63" s="80" t="s">
-        <v>721</v>
-      </c>
-      <c r="AD63" s="23" t="s">
-        <v>722</v>
-      </c>
       <c r="AE63" s="23" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AF63" s="23"/>
       <c r="AG63" s="23"/>
       <c r="AH63" s="23"/>
       <c r="AI63" s="23"/>
       <c r="AJ63" s="23" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AK63" s="101" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AL63" s="23"/>
       <c r="AM63" s="23" t="s">
@@ -10287,7 +10297,7 @@
     </row>
     <row r="64" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B64" s="82">
         <v>2026</v>
@@ -10296,19 +10306,19 @@
         <v>0</v>
       </c>
       <c r="D64" s="61" t="s">
+        <v>723</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="63" t="s">
+        <v>724</v>
+      </c>
+      <c r="G64" s="64" t="s">
         <v>725</v>
       </c>
-      <c r="E64" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="63" t="s">
-        <v>726</v>
-      </c>
-      <c r="G64" s="64" t="s">
-        <v>727</v>
-      </c>
       <c r="H64" s="63" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="I64" s="63" t="s">
         <v>48</v>
@@ -10325,7 +10335,7 @@
         <v>48</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="P64" s="63">
         <v>2</v>
@@ -10366,10 +10376,10 @@
       <c r="AH64" s="63"/>
       <c r="AI64" s="63"/>
       <c r="AJ64" s="63" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AK64" s="102" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="AL64" s="63"/>
       <c r="AM64" s="63" t="s">
@@ -10390,19 +10400,19 @@
         <v>5</v>
       </c>
       <c r="D65" s="37" t="s">
+        <v>729</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>730</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>731</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="G65" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="F65" s="40" t="s">
-        <v>733</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>734</v>
-      </c>
       <c r="H65" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>48</v>
@@ -10411,10 +10421,10 @@
         <v>80</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M65" s="37" t="s">
         <v>62</v>
@@ -10423,7 +10433,7 @@
         <v>50</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="P65" s="37">
         <v>6</v>
@@ -10435,58 +10445,59 @@
         <v>51</v>
       </c>
       <c r="S65" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA65" s="37" t="s">
         <v>50</v>
       </c>
       <c r="AB65" s="37" t="s">
+        <v>736</v>
+      </c>
+      <c r="AD65" s="40" t="s">
+        <v>737</v>
+      </c>
+      <c r="AE65" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="AF65" s="37" t="s">
         <v>738</v>
       </c>
-      <c r="AD65" s="40" t="s">
+      <c r="AJ65" s="37" t="s">
         <v>739</v>
       </c>
-      <c r="AE65" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="AF65" s="37" t="s">
+      <c r="AK65" s="95" t="s">
         <v>740</v>
-      </c>
-      <c r="AJ65" s="37" t="s">
-        <v>741</v>
-      </c>
-      <c r="AK65" s="95" t="s">
-        <v>742</v>
       </c>
       <c r="AM65" s="23" t="s">
         <v>55</v>
       </c>
       <c r="AO65" s="2"/>
+      <c r="AP65"/>
     </row>
     <row r="66" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B66" s="37">
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
+        <v>741</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>742</v>
+      </c>
+      <c r="F66" s="37" t="s">
         <v>743</v>
       </c>
-      <c r="E66" s="37" t="s">
+      <c r="G66" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="O66" s="37" t="s">
         <v>744</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>745</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="O66" s="37" t="s">
-        <v>746</v>
       </c>
       <c r="P66" s="37">
         <v>5</v>
@@ -10504,51 +10515,51 @@
         <v>51</v>
       </c>
       <c r="AB66" s="37" t="s">
+        <v>745</v>
+      </c>
+      <c r="AC66" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD66" s="37" t="s">
+        <v>746</v>
+      </c>
+      <c r="AE66" s="37" t="s">
         <v>747</v>
       </c>
-      <c r="AC66" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD66" s="37" t="s">
+      <c r="AJ66" s="37" t="s">
         <v>748</v>
       </c>
-      <c r="AE66" s="37" t="s">
+      <c r="AK66" s="95" t="s">
         <v>749</v>
       </c>
-      <c r="AJ66" s="37" t="s">
+      <c r="AM66" s="37" t="s">
         <v>750</v>
-      </c>
-      <c r="AK66" s="95" t="s">
-        <v>751</v>
-      </c>
-      <c r="AM66" s="37" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="67" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B67" s="37">
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
+        <v>751</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>752</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="E67" s="37" t="s">
+      <c r="G67" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="H67" s="37" t="s">
+        <v>754</v>
+      </c>
+      <c r="O67" s="37" t="s">
         <v>755</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>756</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>756</v>
-      </c>
-      <c r="O67" s="37" t="s">
-        <v>757</v>
       </c>
       <c r="P67" s="28">
         <v>5</v>
@@ -10566,39 +10577,39 @@
         <v>51</v>
       </c>
       <c r="AB67" s="37" t="s">
+        <v>756</v>
+      </c>
+      <c r="AJ67" s="37" t="s">
+        <v>757</v>
+      </c>
+      <c r="AK67" s="95" t="s">
         <v>758</v>
-      </c>
-      <c r="AJ67" s="37" t="s">
-        <v>759</v>
-      </c>
-      <c r="AK67" s="95" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="68" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B68" s="37">
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
+        <v>759</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>760</v>
+      </c>
+      <c r="F68" s="37" t="s">
         <v>761</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="G68" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="O68" s="37" t="s">
         <v>762</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>763</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="O68" s="37" t="s">
-        <v>764</v>
       </c>
       <c r="P68" s="28">
         <v>5</v>
@@ -10616,40 +10627,40 @@
         <v>51</v>
       </c>
       <c r="AB68" s="37" t="s">
+        <v>763</v>
+      </c>
+      <c r="AJ68" s="37" t="s">
+        <v>764</v>
+      </c>
+      <c r="AK68" s="95" t="s">
         <v>765</v>
-      </c>
-      <c r="AJ68" s="37" t="s">
-        <v>766</v>
-      </c>
-      <c r="AK68" s="95" t="s">
-        <v>767</v>
       </c>
       <c r="AO68" s="2"/>
     </row>
     <row r="69" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B69" s="37">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
+        <v>766</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>767</v>
+      </c>
+      <c r="F69" s="37" t="s">
         <v>768</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="G69" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="I69" s="37" t="s">
         <v>769</v>
       </c>
-      <c r="F69" s="37" t="s">
+      <c r="O69" s="37" t="s">
         <v>770</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>771</v>
-      </c>
-      <c r="O69" s="37" t="s">
-        <v>772</v>
       </c>
       <c r="P69" s="28">
         <v>5</v>
@@ -10667,45 +10678,45 @@
         <v>51</v>
       </c>
       <c r="AB69" s="37" t="s">
+        <v>771</v>
+      </c>
+      <c r="AJ69" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="AK69" s="95" t="s">
         <v>773</v>
       </c>
-      <c r="AJ69" s="37" t="s">
+      <c r="AM69" s="37" t="s">
         <v>774</v>
       </c>
-      <c r="AK69" s="95" t="s">
+      <c r="AN69" s="37" t="s">
         <v>775</v>
-      </c>
-      <c r="AM69" s="37" t="s">
-        <v>776</v>
-      </c>
-      <c r="AN69" s="37" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="70" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B70" s="37">
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>777</v>
+      </c>
+      <c r="F70" s="92" t="s">
         <v>778</v>
       </c>
-      <c r="E70" s="37" t="s">
+      <c r="G70" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="O70" s="37" t="s">
         <v>779</v>
-      </c>
-      <c r="F70" s="92" t="s">
-        <v>780</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="O70" s="37" t="s">
-        <v>781</v>
       </c>
       <c r="P70" s="28">
         <v>4</v>
@@ -10717,19 +10728,19 @@
         <v>51</v>
       </c>
       <c r="S70" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA70" s="37" t="s">
         <v>51</v>
       </c>
       <c r="AB70" s="37" t="s">
+        <v>780</v>
+      </c>
+      <c r="AJ70" s="37" t="s">
+        <v>781</v>
+      </c>
+      <c r="AK70" s="95" t="s">
         <v>782</v>
-      </c>
-      <c r="AJ70" s="37" t="s">
-        <v>783</v>
-      </c>
-      <c r="AK70" s="95" t="s">
-        <v>784</v>
       </c>
       <c r="AP70"/>
     </row>
@@ -10741,16 +10752,16 @@
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
+        <v>783</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="F71" s="109" t="s">
         <v>785</v>
       </c>
-      <c r="E71" s="37" t="s">
-        <v>786</v>
-      </c>
-      <c r="F71" s="109" t="s">
-        <v>846</v>
-      </c>
       <c r="G71" s="37" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H71" s="37" t="s">
         <v>126</v>
@@ -10759,10 +10770,10 @@
         <v>68</v>
       </c>
       <c r="K71" s="49" t="s">
+        <v>415</v>
+      </c>
+      <c r="L71" s="49" t="s">
         <v>416</v>
-      </c>
-      <c r="L71" s="49" t="s">
-        <v>417</v>
       </c>
       <c r="M71" s="49" t="s">
         <v>62</v>
@@ -10771,7 +10782,7 @@
         <v>50</v>
       </c>
       <c r="O71" s="37" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P71" s="28">
         <v>7</v>
@@ -10783,34 +10794,34 @@
         <v>51</v>
       </c>
       <c r="S71" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA71" s="37" t="s">
         <v>51</v>
       </c>
       <c r="AB71" s="37" t="s">
+        <v>787</v>
+      </c>
+      <c r="AE71" s="37" t="s">
         <v>788</v>
       </c>
-      <c r="AE71" s="37" t="s">
+      <c r="AJ71" s="37" t="s">
         <v>789</v>
       </c>
-      <c r="AJ71" s="37" t="s">
+      <c r="AK71" s="95" t="s">
         <v>790</v>
       </c>
-      <c r="AK71" s="95" t="s">
+      <c r="AM71" s="37" t="s">
+        <v>774</v>
+      </c>
+      <c r="AN71" s="37" t="s">
         <v>791</v>
-      </c>
-      <c r="AM71" s="37" t="s">
-        <v>776</v>
-      </c>
-      <c r="AN71" s="37" t="s">
-        <v>792</v>
       </c>
       <c r="AP71"/>
     </row>
     <row r="72" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="78" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B72" s="63">
         <v>2026</v>
@@ -10819,19 +10830,19 @@
         <v>0</v>
       </c>
       <c r="D72" s="63" t="s">
+        <v>792</v>
+      </c>
+      <c r="E72" s="63" t="s">
         <v>793</v>
       </c>
-      <c r="E72" s="63" t="s">
+      <c r="F72" s="76" t="s">
         <v>794</v>
       </c>
-      <c r="F72" s="76" t="s">
+      <c r="G72" s="63" t="s">
         <v>795</v>
       </c>
-      <c r="G72" s="63" t="s">
-        <v>796</v>
-      </c>
       <c r="H72" s="63" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="I72" s="63" t="s">
         <v>48</v>
@@ -10848,7 +10859,7 @@
         <v>48</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P72" s="65">
         <v>6</v>
@@ -10891,10 +10902,10 @@
       <c r="AH72" s="63"/>
       <c r="AI72" s="63"/>
       <c r="AJ72" s="63" t="s">
+        <v>797</v>
+      </c>
+      <c r="AK72" s="102" t="s">
         <v>798</v>
-      </c>
-      <c r="AK72" s="102" t="s">
-        <v>799</v>
       </c>
       <c r="AL72" s="63"/>
       <c r="AM72" s="63" t="s">
@@ -10906,28 +10917,28 @@
     </row>
     <row r="73" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B73" s="37">
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
+        <v>799</v>
+      </c>
+      <c r="E73" s="37" t="s">
         <v>800</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="F73" s="80" t="s">
         <v>801</v>
       </c>
-      <c r="F73" s="80" t="s">
+      <c r="G73" s="37" t="s">
         <v>802</v>
       </c>
-      <c r="G73" s="37" t="s">
+      <c r="H73" s="37" t="s">
+        <v>802</v>
+      </c>
+      <c r="O73" s="37" t="s">
         <v>803</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>803</v>
-      </c>
-      <c r="O73" s="37" t="s">
-        <v>804</v>
       </c>
       <c r="P73" s="28">
         <v>6</v>
@@ -10945,33 +10956,33 @@
         <v>51</v>
       </c>
       <c r="AB73" s="37" t="s">
+        <v>804</v>
+      </c>
+      <c r="AJ73" s="37" t="s">
         <v>805</v>
       </c>
-      <c r="AJ73" s="37" t="s">
+      <c r="AK73" s="95" t="s">
         <v>806</v>
-      </c>
-      <c r="AK73" s="95" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="74" spans="1:42" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B74">
         <v>2026</v>
       </c>
       <c r="D74" t="s">
+        <v>807</v>
+      </c>
+      <c r="E74" t="s">
         <v>808</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" s="92" t="s">
         <v>809</v>
       </c>
-      <c r="F74" s="92" t="s">
+      <c r="O74" t="s">
         <v>810</v>
-      </c>
-      <c r="O74" t="s">
-        <v>811</v>
       </c>
       <c r="P74">
         <v>6</v>
@@ -10994,19 +11005,19 @@
         <v>51</v>
       </c>
       <c r="AB74" t="s">
+        <v>811</v>
+      </c>
+      <c r="AE74" s="37" t="s">
         <v>812</v>
       </c>
-      <c r="AE74" s="37" t="s">
+      <c r="AF74" s="37" t="s">
         <v>813</v>
       </c>
-      <c r="AF74" s="37" t="s">
+      <c r="AJ74" t="s">
         <v>814</v>
       </c>
-      <c r="AJ74" t="s">
+      <c r="AK74" s="103" t="s">
         <v>815</v>
-      </c>
-      <c r="AK74" s="103" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="75" spans="1:42" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -11017,34 +11028,34 @@
         <v>2026</v>
       </c>
       <c r="D75" s="37" t="s">
+        <v>816</v>
+      </c>
+      <c r="E75" t="s">
         <v>817</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" s="92" t="s">
         <v>818</v>
       </c>
-      <c r="F75" s="92" t="s">
+      <c r="G75" s="37" t="s">
         <v>819</v>
       </c>
-      <c r="G75" s="37" t="s">
+      <c r="H75" s="37" t="s">
         <v>820</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>821</v>
       </c>
       <c r="J75" s="37" t="s">
         <v>68</v>
       </c>
       <c r="K75" s="37" t="s">
+        <v>821</v>
+      </c>
+      <c r="L75" s="37" t="s">
         <v>822</v>
-      </c>
-      <c r="L75" s="37" t="s">
-        <v>823</v>
       </c>
       <c r="M75" s="37" t="s">
         <v>62</v>
       </c>
       <c r="O75" s="37" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="P75" s="28">
         <v>6</v>
@@ -11062,24 +11073,23 @@
         <v>51</v>
       </c>
       <c r="AC75" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="AD75" s="92" t="s">
         <v>825</v>
       </c>
-      <c r="AD75" s="92" t="s">
+      <c r="AE75" s="37" t="s">
         <v>826</v>
       </c>
-      <c r="AE75" s="37" t="s">
+      <c r="AK75" s="95" t="s">
         <v>827</v>
-      </c>
-      <c r="AK75" s="95" t="s">
-        <v>828</v>
       </c>
       <c r="AM75" s="37" t="s">
         <v>55</v>
       </c>
       <c r="AN75" s="37" t="s">
-        <v>829</v>
-      </c>
-      <c r="AP75"/>
+        <v>828</v>
+      </c>
     </row>
     <row r="76" spans="1:42" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="79" t="s">
@@ -11089,6 +11099,9 @@
         <v>2026</v>
       </c>
       <c r="D76" s="37" t="s">
+        <v>829</v>
+      </c>
+      <c r="E76" t="s">
         <v>830</v>
       </c>
       <c r="F76" s="37" t="s">
@@ -11107,7 +11120,7 @@
         <v>80</v>
       </c>
       <c r="K76" s="49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L76" s="49" t="s">
         <v>128</v>
@@ -11130,43 +11143,47 @@
       <c r="R76" s="37" t="s">
         <v>51</v>
       </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
       <c r="AC76" s="92" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="AE76" s="37" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="AF76" s="92" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="AM76" s="37" t="s">
         <v>55</v>
       </c>
+      <c r="AP76"/>
     </row>
     <row r="77" spans="1:42" ht="221" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B77" s="37">
         <v>2026</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="E77" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="F77" s="92" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O77" s="37" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="P77" s="28">
         <v>6</v>
@@ -11181,42 +11198,46 @@
         <v>0</v>
       </c>
       <c r="AB77" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="AE77" s="37" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AJ77" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="AK77" s="95" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="AM77" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="AP77" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="78" spans="1:42" ht="102" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+      <c r="AP77"/>
+    </row>
+    <row r="78" spans="1:42" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="79" t="s">
-        <v>377</v>
+        <v>187</v>
       </c>
       <c r="B78" s="37">
         <v>2026</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>840</v>
+        <v>843</v>
+      </c>
+      <c r="E78" t="s">
+        <v>844</v>
+      </c>
+      <c r="F78" t="s">
+        <v>845</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O78" s="37" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="P78" s="28">
         <v>5</v>
@@ -11227,14 +11248,27 @@
       <c r="R78" s="37" t="s">
         <v>51</v>
       </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>51</v>
+      </c>
       <c r="AB78" s="37" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="AE78" s="37" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="79" spans="1:42" ht="409.6" x14ac:dyDescent="0.2">
+        <v>812</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>848</v>
+      </c>
+      <c r="AK78" t="s">
+        <v>849</v>
+      </c>
+      <c r="AP78"/>
+    </row>
+    <row r="79" spans="1:42" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="79" t="s">
         <v>62</v>
       </c>
@@ -11242,25 +11276,25 @@
         <v>2026</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F79" s="92" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J79" s="37" t="s">
         <v>109</v>
       </c>
       <c r="K79" s="49" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="L79" s="37" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M79" s="37" t="s">
         <v>62</v>
@@ -11269,7 +11303,7 @@
         <v>50</v>
       </c>
       <c r="O79" s="37" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="P79" s="28">
         <v>6</v>
@@ -11284,10 +11318,10 @@
         <v>2</v>
       </c>
       <c r="AB79" s="37" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AD79" s="37" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AE79" s="37" t="s">
         <v>859</v>
@@ -11302,11 +11336,58 @@
         <v>55</v>
       </c>
       <c r="AO79" s="37" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="B80" s="37"/>
+        <v>862</v>
+      </c>
+    </row>
+    <row r="80" spans="1:42" ht="119" x14ac:dyDescent="0.2">
+      <c r="A80" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="37">
+        <v>2026</v>
+      </c>
+      <c r="D80" s="37" t="s">
+        <v>863</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>865</v>
+      </c>
+      <c r="G80" s="37" t="s">
+        <v>864</v>
+      </c>
+      <c r="H80" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="J80" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K80" s="37" t="s">
+        <v>866</v>
+      </c>
+      <c r="L80" s="37" t="s">
+        <v>867</v>
+      </c>
+      <c r="M80" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="N80" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="O80" s="37" t="s">
+        <v>868</v>
+      </c>
+      <c r="P80" s="28">
+        <v>7</v>
+      </c>
+      <c r="Q80" s="28">
+        <v>3</v>
+      </c>
+      <c r="R80" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM80" s="37" t="s">
+        <v>774</v>
+      </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B81" s="37"/>
@@ -13916,7 +13997,7 @@
       <c r="B949" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AP1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
@@ -14052,17 +14133,18 @@
     <hyperlink ref="AC63" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
     <hyperlink ref="F65" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
     <hyperlink ref="F70" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F72" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="F73" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="F74" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F75" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="AC75" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="AD75" r:id="rId94" display="https://doi.org/10.5281/zenodo.21380299" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F77" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="AF76" r:id="rId96" display="https://lnkd.in/p/eS8dQ3fZ" xr:uid="{0B677043-826E-834D-868D-4B423761D01A}"/>
-    <hyperlink ref="AC76" r:id="rId97" xr:uid="{3EDB0987-2302-D449-AB7F-B05F134CEDA6}"/>
-    <hyperlink ref="F71" r:id="rId98" xr:uid="{F334CBC2-D676-7F4F-875E-6623C7C54EDA}"/>
-    <hyperlink ref="F79" r:id="rId99" xr:uid="{8440A738-A599-D548-AD62-6630D8D2835B}"/>
+    <hyperlink ref="F71" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F72" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F73" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F74" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F75" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="AC75" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="AD75" r:id="rId95" display="https://doi.org/10.5281/zenodo.21380299" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="AC76" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="AF76" r:id="rId97" display="https://lnkd.in/p/eS8dQ3fZ" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F77" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F79" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F31" r:id="rId100" xr:uid="{8923262E-DF36-674E-823B-CC31E5D9E5F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Library/CloudStorage/OneDrive-UniversidadPolitécnicadeMadrid/Universidad/Publicaciones/00_publications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C88F85C-B454-4740-9C84-47D987D1871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
